--- a/deliverables/AgriPack_Model_final.xlsx
+++ b/deliverables/AgriPack_Model_final.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="1673">
   <si>
     <t xml:space="preserve">Three Statement Model</t>
   </si>
@@ -5067,6 +5067,18 @@
   </si>
   <si>
     <t xml:space="preserve">Nay = vốn cổ phần tăng thêm trong năm (BCĐKT hàng 72).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toàn bộ file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mọi sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công thức chỉ dùng hàm cơ bản: phép cộng dùng SUM; SUBTOTAL(9, …) → SUM (tổng lớn = SUM các tổng con); SUMPRODUCT → NPV (Sensitivity) và MAX/MIN (Checks); INDEX → CHOOSE/IF; N() → liên kết trực tiếp; IF(ISNUMBER(…)) → IF(… = "")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dùng hàm đơn giản nhất có thể để dễ kiểm tra; giá trị mọi ô không đổi (đã so từng ô trước và sau khi đổi).</t>
   </si>
 </sst>
 </file>
@@ -8909,11 +8921,11 @@
       <c r="B5" s="305"/>
       <c r="C5" s="314" t="n">
         <f aca="false">'Pro Forma'!C10-Drivers!F135*MAX(0,'Pro Forma'!C10-Drivers!F133)</f>
-        <v>6712155.6766217</v>
+        <v>6712155.67662171</v>
       </c>
       <c r="D5" s="314" t="n">
         <f aca="false">'Pro Forma'!D10-Drivers!G135*MAX(0,'Pro Forma'!D10-Drivers!G133)</f>
-        <v>7199606.85986841</v>
+        <v>7199606.85986843</v>
       </c>
       <c r="E5" s="314" t="n">
         <f aca="false">'Pro Forma'!E10-Drivers!H135*MAX(0,'Pro Forma'!E10-Drivers!H133)</f>
@@ -8963,11 +8975,11 @@
       <c r="B7" s="305"/>
       <c r="C7" s="314" t="n">
         <f aca="false">'Pro Forma'!C37</f>
-        <v>2584386.32806609</v>
+        <v>2584386.32806608</v>
       </c>
       <c r="D7" s="314" t="n">
         <f aca="false">'Pro Forma'!D37</f>
-        <v>3280215.67477489</v>
+        <v>3280215.6747749</v>
       </c>
       <c r="E7" s="314" t="n">
         <f aca="false">'Pro Forma'!E37</f>
@@ -9028,7 +9040,7 @@
       <c r="B10" s="367"/>
       <c r="C10" s="367" t="n">
         <f aca="false">C5+C6-C7-C8</f>
-        <v>-4864899.64943638</v>
+        <v>-4864899.64943637</v>
       </c>
       <c r="D10" s="367" t="n">
         <f aca="false">D5+D6-D7-D8</f>
@@ -9040,7 +9052,7 @@
       </c>
       <c r="F10" s="367" t="n">
         <f aca="false">F5+F6-F7-F8</f>
-        <v>3623049.12114107</v>
+        <v>3623049.12114108</v>
       </c>
       <c r="G10" s="367" t="n">
         <f aca="false">G5+G6-G7-G8</f>
@@ -9097,7 +9109,7 @@
       <c r="B14" s="368"/>
       <c r="C14" s="377" t="n">
         <f aca="false">C10/(1+Assumption!$D$18)^C3</f>
-        <v>-4281056.32927654</v>
+        <v>-4281056.32927653</v>
       </c>
       <c r="D14" s="377" t="n">
         <f aca="false">D10/(1+Assumption!$D$18)^D3</f>
@@ -9105,15 +9117,15 @@
       </c>
       <c r="E14" s="377" t="n">
         <f aca="false">E10/(1+Assumption!$D$18)^E3</f>
-        <v>-2509990.51366287</v>
+        <v>-2509990.51366288</v>
       </c>
       <c r="F14" s="377" t="n">
         <f aca="false">F10/(1+Assumption!$D$18)^F3</f>
-        <v>2172613.36067415</v>
+        <v>2172613.36067416</v>
       </c>
       <c r="G14" s="378" t="n">
-        <f aca="false">(G10+G12)/(1+Assumption!$D$18)^G3</f>
-        <v>69102240.8629947</v>
+        <f aca="false">SUM(G10,G12)/(1+Assumption!$D$18)^G3</f>
+        <v>69102240.8629948</v>
       </c>
       <c r="H14" s="310"/>
     </row>
@@ -9180,7 +9192,7 @@
       </c>
       <c r="B20" s="390" t="n">
         <f aca="false">B19/B21</f>
-        <v>0.534209356458693</v>
+        <v>0.534209356458692</v>
       </c>
       <c r="C20" s="391"/>
       <c r="D20" s="293"/>
@@ -9190,8 +9202,8 @@
         <v>555</v>
       </c>
       <c r="B21" s="357" t="n">
-        <f aca="false">B22+B19</f>
-        <v>70404538.3017436</v>
+        <f aca="false">SUM(B22,B19)</f>
+        <v>70404538.3017437</v>
       </c>
       <c r="C21" s="392"/>
       <c r="D21" s="293"/>
@@ -9202,7 +9214,7 @@
       </c>
       <c r="B22" s="357" t="n">
         <f aca="false">C16+'Balance Sheet'!G7-'Balance Sheet'!G48-'Balance Sheet'!G61</f>
-        <v>32793775.2037977</v>
+        <v>32793775.2037978</v>
       </c>
       <c r="C22" s="392"/>
       <c r="D22" s="393" t="s">
@@ -9217,7 +9229,7 @@
       </c>
       <c r="G22" s="396" t="n">
         <f aca="false">B20</f>
-        <v>0.534209356458693</v>
+        <v>0.534209356458692</v>
       </c>
       <c r="H22" s="397" t="s">
         <v>559</v>
@@ -9247,7 +9259,7 @@
       </c>
       <c r="B28" s="399" t="n">
         <f aca="false">G12/(1+Assumption!D18)^G3</f>
-        <v>64534073.4088479</v>
+        <v>64534073.408848</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9282,7 +9294,7 @@
         <v>566</v>
       </c>
       <c r="B32" s="399" t="n">
-        <f aca="false">'Balance Sheet'!G48+'Balance Sheet'!G61</f>
+        <f aca="false">SUM('Balance Sheet'!G48,'Balance Sheet'!G61)</f>
         <v>1602600</v>
       </c>
     </row>
@@ -9292,7 +9304,7 @@
       </c>
       <c r="B33" s="399" t="n">
         <f aca="false">B29+B31-B32</f>
-        <v>32793775.2037977</v>
+        <v>32793775.2037978</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9301,7 +9313,7 @@
       </c>
       <c r="B34" s="401" t="n">
         <f aca="false">B29/Drivers!E76</f>
-        <v>4.08894211236575</v>
+        <v>4.08894211236576</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9319,7 +9331,7 @@
       </c>
       <c r="B36" s="401" t="n">
         <f aca="false">B33/'Income Statement'!E80</f>
-        <v>4.98450797806063</v>
+        <v>4.98450797806064</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9345,7 +9357,7 @@
         <v>573</v>
       </c>
       <c r="B39" s="400" t="n">
-        <f aca="false">G5/('Pro Forma'!G24+'Pro Forma'!G36)</f>
+        <f aca="false">G5/SUM('Pro Forma'!G24,'Pro Forma'!G36)</f>
         <v>0.138811531585547</v>
       </c>
     </row>
@@ -9482,7 +9494,7 @@
       </c>
       <c r="B9" s="415" t="n">
         <f aca="false">(1+B7)/(1-B6)^(1/B5)-1</f>
-        <v>0.258614393402926</v>
+        <v>0.258614393402925</v>
       </c>
       <c r="C9" s="409" t="s">
         <v>585</v>
@@ -9509,7 +9521,7 @@
       </c>
       <c r="E11" s="418" t="n">
         <f aca="false">E8-E5</f>
-        <v>25298910.1339209</v>
+        <v>25298910.133921</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9714,7 +9726,7 @@
         <v>609</v>
       </c>
       <c r="B35" s="428" t="n">
-        <f aca="false">'Balance Sheet'!L48+'Balance Sheet'!L61</f>
+        <f aca="false">SUM('Balance Sheet'!L48,'Balance Sheet'!L61)</f>
         <v>20261905.0994109</v>
       </c>
     </row>
@@ -9760,7 +9772,7 @@
       </c>
       <c r="B41" s="400" t="n">
         <f aca="false">(E6*E9/E5)^(1/B5)-1</f>
-        <v>0.258614393402926</v>
+        <v>0.258614393402925</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10538,7 +10550,7 @@
         <v>673</v>
       </c>
       <c r="B32" s="440" t="n">
-        <f aca="false">('Balance Sheet'!G48+'Balance Sheet'!G61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!G48,'Balance Sheet'!G61)/1000000</f>
         <v>1.6026</v>
       </c>
     </row>
@@ -10724,7 +10736,7 @@
         <v>555</v>
       </c>
       <c r="B48" s="452" t="n">
-        <f aca="false">B49+B46</f>
+        <f aca="false">SUM(B49,B46)</f>
         <v>65.3217307925686</v>
       </c>
     </row>
@@ -10855,15 +10867,15 @@
       </c>
       <c r="B5" s="443" t="n">
         <f aca="false">DCF!B22/1000000</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
       <c r="C5" s="443" t="n">
         <f aca="false">DCF!B19/1000000</f>
         <v>37.6107630979458</v>
       </c>
       <c r="D5" s="443" t="n">
-        <f aca="false">B5+C5</f>
-        <v>70.4045383017436</v>
+        <f aca="false">SUM(B5:C5)</f>
+        <v>70.4045383017437</v>
       </c>
       <c r="E5" s="400" t="n">
         <f aca="false">IF(B5&lt;=0,"n.m.",C5/D5)</f>
@@ -10882,14 +10894,14 @@
       </c>
       <c r="B6" s="443" t="n">
         <f aca="false">VCM!E11/1000000</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
       <c r="C6" s="443" t="n">
         <f aca="false">VCM!E5/1000000</f>
         <v>37.6107630979458</v>
       </c>
       <c r="D6" s="443" t="n">
-        <f aca="false">B6+C6</f>
+        <f aca="false">SUM(B6:C6)</f>
         <v>62.9096732318668</v>
       </c>
       <c r="E6" s="400" t="n">
@@ -10916,7 +10928,7 @@
         <v>37.6107630979458</v>
       </c>
       <c r="D7" s="443" t="n">
-        <f aca="false">B7+C7</f>
+        <f aca="false">SUM(B7:C7)</f>
         <v>65.3217307925686</v>
       </c>
       <c r="E7" s="400" t="n">
@@ -10935,23 +10947,23 @@
         <v>711</v>
       </c>
       <c r="B8" s="444" t="n">
-        <f aca="false">(B5*F5+B6*F6+B7*F7)/(F5+F6+F7)</f>
-        <v>28.779267674012</v>
+        <f aca="false">(B5*F5+B6*F6+B7*F7)/SUM(F5:F7)</f>
+        <v>28.7792676740121</v>
       </c>
       <c r="C8" s="444" t="n">
         <f aca="false">C5</f>
         <v>37.6107630979458</v>
       </c>
       <c r="D8" s="444" t="n">
-        <f aca="false">B8+C8</f>
+        <f aca="false">SUM(B8:C8)</f>
         <v>66.3900307719579</v>
       </c>
       <c r="E8" s="457" t="n">
         <f aca="false">IF(B8&lt;=0,"n.m.",C8/D8)</f>
-        <v>0.56651221065305</v>
+        <v>0.566512210653049</v>
       </c>
       <c r="F8" s="458" t="n">
-        <f aca="false">F5+F6+F7</f>
+        <f aca="false">SUM(F5:F7)</f>
         <v>1</v>
       </c>
     </row>
@@ -10966,7 +10978,7 @@
       </c>
       <c r="B10" s="443" t="n">
         <f aca="false">(1-VCM!B6)*B5+VCM!B6*B11</f>
-        <v>25.6707066753786</v>
+        <v>25.6707066753787</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11025,7 +11037,7 @@
       </c>
       <c r="C18" s="444" t="n">
         <f aca="false">B5</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
       <c r="D18" s="443" t="n">
         <f aca="false">MAX(Sensitivity!C7:E9)</f>
@@ -11041,15 +11053,15 @@
       </c>
       <c r="B19" s="443" t="n">
         <f aca="false">MIN(Sensitivity!C16:E18)</f>
-        <v>11.4063572952171</v>
+        <v>11.406357295217</v>
       </c>
       <c r="C19" s="444" t="n">
         <f aca="false">B6</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
       <c r="D19" s="443" t="n">
         <f aca="false">MAX(Sensitivity!C16:E18)</f>
-        <v>40.7642048034216</v>
+        <v>40.7642048034215</v>
       </c>
       <c r="E19" s="247" t="s">
         <v>723</v>
@@ -11085,7 +11097,7 @@
       </c>
       <c r="C21" s="444" t="n">
         <f aca="false">B8</f>
-        <v>28.779267674012</v>
+        <v>28.7792676740121</v>
       </c>
       <c r="D21" s="443" t="n">
         <f aca="false">(D18*F5+D19*F6+D20*F7)/F8</f>
@@ -11115,7 +11127,7 @@
       </c>
       <c r="B25" s="457" t="n">
         <f aca="false">E8</f>
-        <v>0.56651221065305</v>
+        <v>0.566512210653049</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11132,7 +11144,7 @@
         <v>732</v>
       </c>
       <c r="B27" s="443" t="n">
-        <f aca="false">B24+B26</f>
+        <f aca="false">SUM(B24,B26)</f>
         <v>68.7096049302973</v>
       </c>
     </row>
@@ -11272,7 +11284,7 @@
       </c>
       <c r="B37" s="444" t="n">
         <f aca="false">SUM(DCF!C10:G10)/1000000</f>
-        <v>-38.9101417044817</v>
+        <v>-38.9101417044818</v>
       </c>
       <c r="C37" s="459" t="n">
         <v>-48.9284577387253</v>
@@ -11368,7 +11380,7 @@
       </c>
       <c r="B41" s="444" t="n">
         <f aca="false">B5</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
       <c r="C41" s="459" t="n">
         <v>-50.0071355842633</v>
@@ -11392,7 +11404,7 @@
       </c>
       <c r="B42" s="444" t="n">
         <f aca="false">B6</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
       <c r="C42" s="459" t="n">
         <v>-28.2961982474944</v>
@@ -11416,7 +11428,7 @@
       </c>
       <c r="B43" s="444" t="n">
         <f aca="false">B8</f>
-        <v>28.779267674012</v>
+        <v>28.7792676740121</v>
       </c>
       <c r="C43" s="459" t="n">
         <v>-25.7791399937785</v>
@@ -11440,7 +11452,7 @@
       </c>
       <c r="B44" s="457" t="n">
         <f aca="false">E8</f>
-        <v>0.56651221065305</v>
+        <v>0.566512210653049</v>
       </c>
       <c r="C44" s="460" t="s">
         <v>751</v>
@@ -11463,7 +11475,7 @@
         <v>752</v>
       </c>
       <c r="B45" s="457" t="n">
-        <f aca="false">IF(ISNUMBER(E8),1-E8,"n.m.")</f>
+        <f aca="false">IF(B8&lt;=0,"n.m.",1-E8)</f>
         <v>0.433487789346951</v>
       </c>
       <c r="C45" s="460" t="s">
@@ -11971,24 +11983,24 @@
         <v>0.116378331713872</v>
       </c>
       <c r="B6" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A6)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A6-B$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>52.1978032793631</v>
+        <f aca="false">(NPV($A6,DCF!$C$10:$G$10)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A6-B$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>52.1978032793632</v>
       </c>
       <c r="C6" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A6)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A6-C$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>55.3308961937083</v>
+        <f aca="false">(NPV($A6,DCF!$C$10:$G$10)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A6-C$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>55.3308961937084</v>
       </c>
       <c r="D6" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A6)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A6-D$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>59.2111674360915</v>
+        <f aca="false">(NPV($A6,DCF!$C$10:$G$10)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A6-D$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>59.2111674360916</v>
       </c>
       <c r="E6" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A6)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A6-E$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>64.2362050365185</v>
+        <f aca="false">(NPV($A6,DCF!$C$10:$G$10)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A6-E$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>64.2362050365187</v>
       </c>
       <c r="F6" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A6)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A6-F$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>71.1465054611667</v>
+        <f aca="false">(NPV($A6,DCF!$C$10:$G$10)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A6-F$5))/(1+$A6)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>71.1465054611668</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11997,23 +12009,23 @@
         <v>0.126378331713872</v>
       </c>
       <c r="B7" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A7)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A7-B$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>40.5042160819163</v>
+        <f aca="false">(NPV($A7,DCF!$C$10:$G$10)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A7-B$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>40.5042160819164</v>
       </c>
       <c r="C7" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A7)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A7-C$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A7,DCF!$C$10:$G$10)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A7-C$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>42.1800193539711</v>
       </c>
       <c r="D7" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A7)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A7-D$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>44.1310371374378</v>
+        <f aca="false">(NPV($A7,DCF!$C$10:$G$10)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A7-D$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>44.1310371374379</v>
       </c>
       <c r="E7" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A7)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A7-E$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A7,DCF!$C$10:$G$10)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A7-E$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>46.4816539284192</v>
       </c>
       <c r="F7" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A7)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A7-F$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A7,DCF!$C$10:$G$10)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A7-F$5))/(1+$A7)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>49.4445040823671</v>
       </c>
     </row>
@@ -12023,24 +12035,24 @@
         <v>0.136378331713872</v>
       </c>
       <c r="B8" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A8)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A8-B$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A8,DCF!$C$10:$G$10)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A8-B$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>31.238476193677</v>
       </c>
       <c r="C8" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A8)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A8-C$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>31.9974619633138</v>
+        <f aca="false">(NPV($A8,DCF!$C$10:$G$10)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A8-C$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>31.9974619633139</v>
       </c>
       <c r="D8" s="463" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A8)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A8-D$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>32.7937752037977</v>
+        <f aca="false">(NPV($A8,DCF!$C$10:$G$10)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A8-D$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>32.7937752037978</v>
       </c>
       <c r="E8" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A8)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A8-E$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>33.6420774572218</v>
+        <f aca="false">(NPV($A8,DCF!$C$10:$G$10)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A8-E$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>33.6420774572219</v>
       </c>
       <c r="F8" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A8)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A8-F$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>34.5658654031187</v>
+        <f aca="false">(NPV($A8,DCF!$C$10:$G$10)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A8-F$5))/(1+$A8)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>34.5658654031188</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12049,23 +12061,23 @@
         <v>0.146378331713872</v>
       </c>
       <c r="B9" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A9)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A9-B$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A9,DCF!$C$10:$G$10)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A9-B$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>23.7649322155348</v>
       </c>
       <c r="C9" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A9)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A9-C$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A9,DCF!$C$10:$G$10)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A9-C$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>23.9361926590634</v>
       </c>
       <c r="D9" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A9)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A9-D$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A9,DCF!$C$10:$G$10)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A9-D$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>24.0242622397062</v>
       </c>
       <c r="E9" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A9)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A9-E$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A9,DCF!$C$10:$G$10)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A9-E$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>24.0002479951074</v>
       </c>
       <c r="F9" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A9)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A9-F$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A9,DCF!$C$10:$G$10)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A9-F$5))/(1+$A9)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>23.8201254659498</v>
       </c>
     </row>
@@ -12075,23 +12087,23 @@
         <v>0.156378331713872</v>
       </c>
       <c r="B10" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A10)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A10-B$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A10,DCF!$C$10:$G$10)+(DCF!$G$5*(1+B$5)*(1-B$5/Assumption!$D$19)/($A10-B$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>17.6496259251526</v>
       </c>
       <c r="C10" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A10)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A10-C$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>17.4408061810752</v>
+        <f aca="false">(NPV($A10,DCF!$C$10:$G$10)+(DCF!$G$5*(1+C$5)*(1-C$5/Assumption!$D$19)/($A10-C$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>17.4408061810753</v>
       </c>
       <c r="D10" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A10)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A10-D$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A10,DCF!$C$10:$G$10)+(DCF!$G$5*(1+D$5)*(1-D$5/Assumption!$D$19)/($A10-D$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>17.0897290240432</v>
       </c>
       <c r="E10" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A10)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A10-E$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>16.5521135216854</v>
+        <f aca="false">(NPV($A10,DCF!$C$10:$G$10)+(DCF!$G$5*(1+E$5)*(1-E$5/Assumption!$D$19)/($A10-E$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>16.5521135216855</v>
       </c>
       <c r="F10" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A10)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A10-F$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A10,DCF!$C$10:$G$10)+(DCF!$G$5*(1+F$5)*(1-F$5/Assumption!$D$19)/($A10-F$5))/(1+$A10)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>15.7631731673779</v>
       </c>
     </row>
@@ -12135,7 +12147,7 @@
       </c>
       <c r="B15" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+B$14)*(1-$A15)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>13.7654700414121</v>
+        <v>13.765470041412</v>
       </c>
       <c r="C15" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+C$14)*(1-$A15)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
@@ -12172,7 +12184,7 @@
       </c>
       <c r="E16" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+E$14)*(1-$A16)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>40.7642048034216</v>
+        <v>40.7642048034215</v>
       </c>
       <c r="F16" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+F$14)*(1-$A16)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
@@ -12210,15 +12222,15 @@
       </c>
       <c r="B18" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+B$14)*(1-$A18)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>2.75627722583538</v>
+        <v>2.75627722583537</v>
       </c>
       <c r="C18" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+C$14)*(1-$A18)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>11.4063572952171</v>
+        <v>11.406357295217</v>
       </c>
       <c r="D18" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+D$14)*(1-$A18)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>20.0564373645988</v>
+        <v>20.0564373645987</v>
       </c>
       <c r="E18" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+E$14)*(1-$A18)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
@@ -12235,11 +12247,11 @@
       </c>
       <c r="B19" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+B$14)*(1-$A19)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>-0.91345371269019</v>
+        <v>-0.913453712690204</v>
       </c>
       <c r="C19" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+C$14)*(1-$A19)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>6.95025544129316</v>
+        <v>6.95025544129314</v>
       </c>
       <c r="D19" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+D$14)*(1-$A19)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
@@ -12247,7 +12259,7 @@
       </c>
       <c r="E19" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+E$14)*(1-$A19)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
-        <v>22.6776737492599</v>
+        <v>22.6776737492598</v>
       </c>
       <c r="F19" s="288" t="n">
         <f aca="false">(VCM!$E$6*(1+F$14)*(1-$A19)/(1+VCM!$B$7)^VCM!$B$5-VCM!$E$5)/1000000</f>
@@ -12299,24 +12311,24 @@
         <v>0.116378331713872</v>
       </c>
       <c r="B24" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A24)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>38.2951839338821</v>
+        <f aca="false">(NPV($A24,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>38.2951839338822</v>
       </c>
       <c r="C24" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A24)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>50.5136094764786</v>
+        <f aca="false">(NPV($A24,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>50.5136094764787</v>
       </c>
       <c r="D24" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A24)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>59.2111674360915</v>
+        <f aca="false">(NPV($A24,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>59.2111674360916</v>
       </c>
       <c r="E24" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A24)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>65.7180638303185</v>
+        <f aca="false">(NPV($A24,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>65.7180638303186</v>
       </c>
       <c r="F24" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A24)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>70.7693725817287</v>
+        <f aca="false">(NPV($A24,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A24-Assumption!$D$16))/(1+$A24)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>70.7693725817288</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12325,23 +12337,23 @@
         <v>0.126378331713872</v>
       </c>
       <c r="B25" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A25)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A25,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>26.7462246196837</v>
       </c>
       <c r="C25" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A25)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>36.9018569043305</v>
+        <f aca="false">(NPV($A25,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>36.9018569043306</v>
       </c>
       <c r="D25" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A25)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>44.1310371374378</v>
+        <f aca="false">(NPV($A25,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>44.1310371374379</v>
       </c>
       <c r="E25" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A25)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A25,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>49.5393973933225</v>
       </c>
       <c r="F25" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A25)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A25,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A25-Assumption!$D$16))/(1+$A25)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>53.7379116828026</v>
       </c>
     </row>
@@ -12351,24 +12363,24 @@
         <v>0.136378331713872</v>
       </c>
       <c r="B26" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A26)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>18.0861659289313</v>
+        <f aca="false">(NPV($A26,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>18.0861659289314</v>
       </c>
       <c r="C26" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A26)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>26.6778646561547</v>
+        <f aca="false">(NPV($A26,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>26.6778646561548</v>
       </c>
       <c r="D26" s="463" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A26)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>32.7937752037977</v>
+        <f aca="false">(NPV($A26,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>32.7937752037978</v>
       </c>
       <c r="E26" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A26)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>37.3692659880689</v>
+        <f aca="false">(NPV($A26,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>37.3692659880691</v>
       </c>
       <c r="F26" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A26)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>40.9212230564328</v>
+        <f aca="false">(NPV($A26,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A26-Assumption!$D$16))/(1+$A26)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>40.9212230564329</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12377,24 +12389,24 @@
         <v>0.146378331713872</v>
       </c>
       <c r="B27" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A27)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A27,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>11.40766124909</v>
       </c>
       <c r="C27" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A27)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A27,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>18.7778621190711</v>
       </c>
       <c r="D27" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A27)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A27,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>24.0242622397062</v>
       </c>
       <c r="E27" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A27)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A27,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>27.9492469522142</v>
       </c>
       <c r="F27" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A27)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>30.9962156491544</v>
+        <f aca="false">(NPV($A27,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A27-Assumption!$D$16))/(1+$A27)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>30.9962156491545</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12403,24 +12415,24 @@
         <v>0.156378331713872</v>
       </c>
       <c r="B28" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A28)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A28,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/B$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>6.14490672490059</v>
       </c>
       <c r="C28" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A28)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A28,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/C$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>12.5385097952462</v>
       </c>
       <c r="D28" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A28)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A28,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/D$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>17.0897290240432</v>
       </c>
       <c r="E28" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A28)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <f aca="false">(NPV($A28,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/E$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
         <v>20.4946286667601</v>
       </c>
       <c r="F28" s="288" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$10:$G$10,1/(1+$A28)^DCF!$C$3:$G$3)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
-        <v>23.1378549179401</v>
+        <f aca="false">(NPV($A28,DCF!$C$10:$G$10)+(DCF!$G$5*(1+Assumption!$D$16)*(1-Assumption!$D$16/F$23)/($A28-Assumption!$D$16))/(1+$A28)^DCF!$G$3+'Balance Sheet'!$G$7-'Balance Sheet'!$G$48-'Balance Sheet'!$G$61)/1000000</f>
+        <v>23.1378549179402</v>
       </c>
     </row>
   </sheetData>
@@ -12499,7 +12511,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B4:F4))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B4:F4)=0,MIN(B4:F4)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12528,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B5:F5))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B5:F5)=0,MIN(B5:F5)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12557,7 +12569,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B6:F6))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B6:F6)=0,MIN(B6:F6)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12586,7 +12598,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B7:F7))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B7:F7)=0,MIN(B7:F7)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12615,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B8:F8))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B8:F8)=0,MIN(B8:F8)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12644,7 +12656,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B9:F9))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B9:F9)=0,MIN(B9:F9)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12673,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B10:F10))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B10:F10)=0,MIN(B10:F10)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12682,27 +12694,27 @@
         <v>804</v>
       </c>
       <c r="B11" s="281" t="n">
-        <f aca="false">ROUND(Drivers!F95+'Cash Flow Statement'!F22,0)</f>
+        <f aca="false">ROUND(SUM(Drivers!F95,'Cash Flow Statement'!F22),0)</f>
         <v>0</v>
       </c>
       <c r="C11" s="281" t="n">
-        <f aca="false">ROUND(Drivers!G95+'Cash Flow Statement'!G22,0)</f>
+        <f aca="false">ROUND(SUM(Drivers!G95,'Cash Flow Statement'!G22),0)</f>
         <v>0</v>
       </c>
       <c r="D11" s="281" t="n">
-        <f aca="false">ROUND(Drivers!H95+'Cash Flow Statement'!H22,0)</f>
+        <f aca="false">ROUND(SUM(Drivers!H95,'Cash Flow Statement'!H22),0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="281" t="n">
-        <f aca="false">ROUND(Drivers!I95+'Cash Flow Statement'!I22,0)</f>
+        <f aca="false">ROUND(SUM(Drivers!I95,'Cash Flow Statement'!I22),0)</f>
         <v>0</v>
       </c>
       <c r="F11" s="281" t="n">
-        <f aca="false">ROUND(Drivers!J95+'Cash Flow Statement'!J22,0)</f>
+        <f aca="false">ROUND(SUM(Drivers!J95,'Cash Flow Statement'!J22),0)</f>
         <v>0</v>
       </c>
       <c r="G11" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B11:F11))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B11:F11)=0,MIN(B11:F11)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12731,7 +12743,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="198" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(B12:F12))=0,"OK","LỖI")</f>
+        <f aca="false">IF(AND(MAX(B12:F12)=0,MIN(B12:F12)=0),"OK","LỖI")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12740,7 +12752,7 @@
         <v>806</v>
       </c>
       <c r="B13" s="239" t="n">
-        <f aca="false">INDEX(Drivers!F93:J93,Drivers!C4-2025)</f>
+        <f aca="false">IF(Drivers!C4=2027,Drivers!G93,Drivers!H93)</f>
         <v>0.65</v>
       </c>
       <c r="G13" s="198" t="str">
@@ -14199,7 +14211,7 @@
       </c>
       <c r="F84" s="471" t="n">
         <f aca="false">Drivers!G40</f>
-        <v>0.252329824918865</v>
+        <v>0.252329824918866</v>
       </c>
       <c r="G84" s="471" t="n">
         <f aca="false">Drivers!H40</f>
@@ -14285,7 +14297,7 @@
       </c>
       <c r="C90" s="470" t="n">
         <f aca="false">Summary!C18</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
       <c r="D90" s="470" t="n">
         <f aca="false">Summary!D18</f>
@@ -14298,15 +14310,15 @@
       </c>
       <c r="B91" s="470" t="n">
         <f aca="false">Summary!B19</f>
-        <v>11.4063572952171</v>
+        <v>11.406357295217</v>
       </c>
       <c r="C91" s="470" t="n">
         <f aca="false">Summary!C19</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
       <c r="D91" s="470" t="n">
         <f aca="false">Summary!D19</f>
-        <v>40.7642048034216</v>
+        <v>40.7642048034215</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14336,7 +14348,7 @@
       </c>
       <c r="C93" s="470" t="n">
         <f aca="false">Summary!C21</f>
-        <v>28.779267674012</v>
+        <v>28.7792676740121</v>
       </c>
       <c r="D93" s="470" t="n">
         <f aca="false">Summary!D21</f>
@@ -14446,7 +14458,7 @@
       </c>
       <c r="F100" s="471" t="n">
         <f aca="false">Drivers!G40</f>
-        <v>0.252329824918865</v>
+        <v>0.252329824918866</v>
       </c>
       <c r="G100" s="471" t="n">
         <f aca="false">Drivers!H40</f>
@@ -14594,7 +14606,7 @@
       </c>
       <c r="F104" s="470" t="n">
         <f aca="false">'Income Statement'!F80/1000000</f>
-        <v>5.82744518657437</v>
+        <v>5.82744518657436</v>
       </c>
       <c r="G104" s="470" t="n">
         <f aca="false">'Income Statement'!G80/1000000</f>
@@ -14614,20 +14626,20 @@
         <v>1073</v>
       </c>
       <c r="B105" s="472" t="n">
-        <f aca="false">('Cash Flow Statement'!C19+'Cash Flow Statement'!C22)/1000000</f>
+        <f aca="false">SUM('Cash Flow Statement'!C19,'Cash Flow Statement'!C22)/1000000</f>
         <v>-8.9660112</v>
       </c>
       <c r="C105" s="472" t="n">
-        <f aca="false">('Cash Flow Statement'!D19+'Cash Flow Statement'!D22)/1000000</f>
+        <f aca="false">SUM('Cash Flow Statement'!D19,'Cash Flow Statement'!D22)/1000000</f>
         <v>-5.60845625</v>
       </c>
       <c r="D105" s="472" t="n">
-        <f aca="false">('Cash Flow Statement'!E19+'Cash Flow Statement'!E22)/1000000</f>
+        <f aca="false">SUM('Cash Flow Statement'!E19,'Cash Flow Statement'!E22)/1000000</f>
         <v>1.1979492155</v>
       </c>
       <c r="E105" s="472" t="n">
         <f aca="false">DCF!C10/1000000</f>
-        <v>-4.86489964943638</v>
+        <v>-4.86489964943637</v>
       </c>
       <c r="F105" s="472" t="n">
         <f aca="false">DCF!D10/1000000</f>
@@ -14639,7 +14651,7 @@
       </c>
       <c r="H105" s="472" t="n">
         <f aca="false">DCF!F10/1000000</f>
-        <v>3.62304912114107</v>
+        <v>3.62304912114108</v>
       </c>
       <c r="I105" s="472" t="n">
         <f aca="false">DCF!G10/1000000</f>
@@ -14688,27 +14700,27 @@
         <v>1075</v>
       </c>
       <c r="D107" s="473" t="n">
-        <f aca="false">('Income Statement'!D65*(1-Assumption!$D$15))/(Drivers!E100+Drivers!E114)</f>
+        <f aca="false">('Income Statement'!D65*(1-Assumption!$D$15))/SUM(Drivers!E100,Drivers!E114)</f>
         <v>0.12744318375483</v>
       </c>
       <c r="E107" s="473" t="n">
-        <f aca="false">DCF!C5/(Drivers!F100+Drivers!F114)</f>
+        <f aca="false">DCF!C5/SUM(Drivers!F100,Drivers!F114)</f>
         <v>0.16689273549338</v>
       </c>
       <c r="F107" s="473" t="n">
-        <f aca="false">DCF!D5/(Drivers!G100+Drivers!G114)</f>
-        <v>0.0799425729606493</v>
+        <f aca="false">DCF!D5/SUM(Drivers!G100,Drivers!G114)</f>
+        <v>0.0799425729606494</v>
       </c>
       <c r="G107" s="473" t="n">
-        <f aca="false">DCF!E5/(Drivers!H100+Drivers!H114)</f>
+        <f aca="false">DCF!E5/SUM(Drivers!H100,Drivers!H114)</f>
         <v>0.0507708980889596</v>
       </c>
       <c r="H107" s="473" t="n">
-        <f aca="false">DCF!F5/(Drivers!I100+Drivers!I114)</f>
+        <f aca="false">DCF!F5/SUM(Drivers!I100,Drivers!I114)</f>
         <v>0.104296417970394</v>
       </c>
       <c r="I107" s="473" t="n">
-        <f aca="false">DCF!G5/(Drivers!J100+Drivers!J114)</f>
+        <f aca="false">DCF!G5/SUM(Drivers!J100,Drivers!J114)</f>
         <v>0.138811531585547</v>
       </c>
     </row>
@@ -14730,7 +14742,7 @@
       </c>
       <c r="E108" s="470" t="n">
         <f aca="false">'Balance Sheet'!H76/1000000</f>
-        <v>74.1621107400675</v>
+        <v>74.1621107400676</v>
       </c>
       <c r="F108" s="470" t="n">
         <f aca="false">'Balance Sheet'!I76/1000000</f>
@@ -14754,35 +14766,35 @@
         <v>1077</v>
       </c>
       <c r="B109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!E48+'Balance Sheet'!E61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!E48,'Balance Sheet'!E61)/1000000</f>
         <v>1.29</v>
       </c>
       <c r="C109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!F48+'Balance Sheet'!F61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!F48,'Balance Sheet'!F61)/1000000</f>
         <v>1.608</v>
       </c>
       <c r="D109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!G48+'Balance Sheet'!G61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!G48,'Balance Sheet'!G61)/1000000</f>
         <v>1.6026</v>
       </c>
       <c r="E109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!H48+'Balance Sheet'!H61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!H48,'Balance Sheet'!H61)/1000000</f>
         <v>1.6026</v>
       </c>
       <c r="F109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!I48+'Balance Sheet'!I61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!I48,'Balance Sheet'!I61)/1000000</f>
         <v>32.7014418323515</v>
       </c>
       <c r="G109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!J48+'Balance Sheet'!J61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!J48,'Balance Sheet'!J61)/1000000</f>
         <v>32.7014418323515</v>
       </c>
       <c r="H109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!K48+'Balance Sheet'!K61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!K48,'Balance Sheet'!K61)/1000000</f>
         <v>26.4816734658812</v>
       </c>
       <c r="I109" s="470" t="n">
-        <f aca="false">('Balance Sheet'!L48+'Balance Sheet'!L61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!L48,'Balance Sheet'!L61)/1000000</f>
         <v>20.2619050994109</v>
       </c>
     </row>
@@ -15620,7 +15632,7 @@
       </c>
       <c r="D185" s="473" t="n">
         <f aca="false">'Income Statement'!D65/'Income Statement'!D13</f>
-        <v>0.0959623635589914</v>
+        <v>0.0959623635589913</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15654,7 +15666,7 @@
       </c>
       <c r="D187" s="473" t="n">
         <f aca="false">'Income Statement'!D80/'Income Statement'!D13</f>
-        <v>0.0929719874856646</v>
+        <v>0.0929719874856645</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15662,15 +15674,15 @@
         <v>1158</v>
       </c>
       <c r="B188" s="473" t="n">
-        <f aca="false">'Income Statement'!B80/(('Balance Sheet'!E76+'Balance Sheet'!D76)/2)</f>
+        <f aca="false">'Income Statement'!B80/(SUM('Balance Sheet'!E76,'Balance Sheet'!D76)/2)</f>
         <v>-0.251115277615639</v>
       </c>
       <c r="C188" s="473" t="n">
-        <f aca="false">'Income Statement'!C80/(('Balance Sheet'!F76+'Balance Sheet'!E76)/2)</f>
+        <f aca="false">'Income Statement'!C80/(SUM('Balance Sheet'!F76,'Balance Sheet'!E76)/2)</f>
         <v>-0.0225650512039039</v>
       </c>
       <c r="D188" s="473" t="n">
-        <f aca="false">'Income Statement'!D80/(('Balance Sheet'!G76+'Balance Sheet'!F76)/2)</f>
+        <f aca="false">'Income Statement'!D80/(SUM('Balance Sheet'!G76,'Balance Sheet'!F76)/2)</f>
         <v>0.159228497929602</v>
       </c>
     </row>
@@ -15679,15 +15691,15 @@
         <v>1159</v>
       </c>
       <c r="B189" s="473" t="n">
-        <f aca="false">'Income Statement'!B80/(('Balance Sheet'!E34+'Balance Sheet'!D34)/2)</f>
+        <f aca="false">'Income Statement'!B80/(SUM('Balance Sheet'!E34,'Balance Sheet'!D34)/2)</f>
         <v>-0.231245874185055</v>
       </c>
       <c r="C189" s="473" t="n">
-        <f aca="false">'Income Statement'!C80/(('Balance Sheet'!F34+'Balance Sheet'!E34)/2)</f>
+        <f aca="false">'Income Statement'!C80/(SUM('Balance Sheet'!F34,'Balance Sheet'!E34)/2)</f>
         <v>-0.0209824588632599</v>
       </c>
       <c r="D189" s="473" t="n">
-        <f aca="false">'Income Statement'!D80/(('Balance Sheet'!G34+'Balance Sheet'!F34)/2)</f>
+        <f aca="false">'Income Statement'!D80/(SUM('Balance Sheet'!G34,'Balance Sheet'!F34)/2)</f>
         <v>0.14898647603738</v>
       </c>
     </row>
@@ -15696,15 +15708,15 @@
         <v>1160</v>
       </c>
       <c r="B190" s="482" t="n">
-        <f aca="false">'Income Statement'!B13/(('Balance Sheet'!E34+'Balance Sheet'!D34)/2)</f>
+        <f aca="false">'Income Statement'!B13/(SUM('Balance Sheet'!E34,'Balance Sheet'!D34)/2)</f>
         <v>1.04316572707421</v>
       </c>
       <c r="C190" s="482" t="n">
-        <f aca="false">'Income Statement'!C13/(('Balance Sheet'!F34+'Balance Sheet'!E34)/2)</f>
+        <f aca="false">'Income Statement'!C13/(SUM('Balance Sheet'!F34,'Balance Sheet'!E34)/2)</f>
         <v>1.28945378949171</v>
       </c>
       <c r="D190" s="482" t="n">
-        <f aca="false">'Income Statement'!D13/(('Balance Sheet'!G34+'Balance Sheet'!F34)/2)</f>
+        <f aca="false">'Income Statement'!D13/(SUM('Balance Sheet'!G34,'Balance Sheet'!F34)/2)</f>
         <v>1.60248780376296</v>
       </c>
     </row>
@@ -16174,15 +16186,15 @@
         <v>1182</v>
       </c>
       <c r="B235" s="479" t="n">
-        <f aca="false">'Cash Flow Statement'!C19+'Cash Flow Statement'!C22</f>
+        <f aca="false">SUM('Cash Flow Statement'!C19,'Cash Flow Statement'!C22)</f>
         <v>-8966011.2</v>
       </c>
       <c r="C235" s="479" t="n">
-        <f aca="false">'Cash Flow Statement'!D19+'Cash Flow Statement'!D22</f>
+        <f aca="false">SUM('Cash Flow Statement'!D19,'Cash Flow Statement'!D22)</f>
         <v>-5608456.25</v>
       </c>
       <c r="D235" s="479" t="n">
-        <f aca="false">'Cash Flow Statement'!E19+'Cash Flow Statement'!E22</f>
+        <f aca="false">SUM('Cash Flow Statement'!E19,'Cash Flow Statement'!E22)</f>
         <v>1197949.2155</v>
       </c>
     </row>
@@ -18364,7 +18376,7 @@
       </c>
       <c r="D406" s="473" t="n">
         <f aca="false">'Income Statement'!D65/'Income Statement'!D13</f>
-        <v>0.0959623635589914</v>
+        <v>0.0959623635589913</v>
       </c>
       <c r="E406" s="473" t="n">
         <f aca="false">'Income Statement'!E65/'Income Statement'!E13</f>
@@ -18401,7 +18413,7 @@
       </c>
       <c r="D407" s="473" t="n">
         <f aca="false">'Income Statement'!D80/'Income Statement'!D13</f>
-        <v>0.0929719874856646</v>
+        <v>0.0929719874856645</v>
       </c>
       <c r="E407" s="473" t="n">
         <f aca="false">'Income Statement'!E80/'Income Statement'!E13</f>
@@ -18421,7 +18433,7 @@
       </c>
       <c r="I407" s="473" t="n">
         <f aca="false">'Income Statement'!I80/'Income Statement'!I13</f>
-        <v>0.081346238218807</v>
+        <v>0.0813462382188069</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18537,7 +18549,7 @@
       </c>
       <c r="D414" s="471" t="n">
         <f aca="false">Drivers!G40</f>
-        <v>0.252329824918865</v>
+        <v>0.252329824918866</v>
       </c>
       <c r="E414" s="471" t="n">
         <f aca="false">Drivers!H40</f>
@@ -18682,7 +18694,7 @@
       </c>
       <c r="D419" s="470" t="n">
         <f aca="false">'Income Statement'!F65/1000000</f>
-        <v>8.99950857483553</v>
+        <v>8.99950857483552</v>
       </c>
       <c r="E419" s="470" t="n">
         <f aca="false">'Income Statement'!G65/1000000</f>
@@ -18740,7 +18752,7 @@
       </c>
       <c r="D421" s="470" t="n">
         <f aca="false">'Income Statement'!F76/1000000</f>
-        <v>7.28430648321796</v>
+        <v>7.28430648321795</v>
       </c>
       <c r="E421" s="470" t="n">
         <f aca="false">'Income Statement'!G76/1000000</f>
@@ -18798,7 +18810,7 @@
       </c>
       <c r="D423" s="470" t="n">
         <f aca="false">'Income Statement'!F80/1000000</f>
-        <v>5.82744518657437</v>
+        <v>5.82744518657436</v>
       </c>
       <c r="E423" s="470" t="n">
         <f aca="false">'Income Statement'!G80/1000000</f>
@@ -18819,7 +18831,7 @@
       </c>
       <c r="B424" s="473" t="n">
         <f aca="false">'Income Statement'!D80/'Income Statement'!D13</f>
-        <v>0.0929719874856646</v>
+        <v>0.0929719874856645</v>
       </c>
       <c r="C424" s="473" t="n">
         <f aca="false">'Income Statement'!E80/'Income Statement'!E13</f>
@@ -18839,7 +18851,7 @@
       </c>
       <c r="G424" s="473" t="n">
         <f aca="false">'Income Statement'!I80/'Income Statement'!I13</f>
-        <v>0.081346238218807</v>
+        <v>0.0813462382188069</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19004,11 +19016,11 @@
         <v>0.295972934449596</v>
       </c>
       <c r="J432" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H432),H432/SUM(E432:G432),"")</f>
+        <f aca="false">IF(H432="","",H432/SUM(E432:G432))</f>
         <v>0.0172682143617806</v>
       </c>
       <c r="K432" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H432),SUM(B432:D432)/H432,"")</f>
+        <f aca="false">IF(H432="","",SUM(B432:D432)/H432)</f>
         <v>17.1397533206831</v>
       </c>
     </row>
@@ -19042,11 +19054,11 @@
         <v>0.0885344979707076</v>
       </c>
       <c r="J433" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H433),H433/SUM(E433:G433),"")</f>
+        <f aca="false">IF(H433="","",H433/SUM(E433:G433))</f>
         <v>0.0208730368801835</v>
       </c>
       <c r="K433" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H433),SUM(B433:D433)/H433,"")</f>
+        <f aca="false">IF(H433="","",SUM(B433:D433)/H433)</f>
         <v>4.24157244002959</v>
       </c>
     </row>
@@ -19080,11 +19092,11 @@
         <v>0.0859752351114531</v>
       </c>
       <c r="J434" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H434),H434/SUM(E434:G434),"")</f>
+        <f aca="false">IF(H434="","",H434/SUM(E434:G434))</f>
         <v>0.0342108613465147</v>
       </c>
       <c r="K434" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H434),SUM(B434:D434)/H434,"")</f>
+        <f aca="false">IF(H434="","",SUM(B434:D434)/H434)</f>
         <v>2.51309764582154</v>
       </c>
     </row>
@@ -19118,11 +19130,11 @@
         <v>0.0830597782835477</v>
       </c>
       <c r="J435" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H435),H435/SUM(E435:G435),"")</f>
+        <f aca="false">IF(H435="","",H435/SUM(E435:G435))</f>
         <v>0.0387555188337329</v>
       </c>
       <c r="K435" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H435),SUM(B435:D435)/H435,"")</f>
+        <f aca="false">IF(H435="","",SUM(B435:D435)/H435)</f>
         <v>2.14317291531786</v>
       </c>
     </row>
@@ -19156,11 +19168,11 @@
         <v>0.0824308266847734</v>
       </c>
       <c r="J436" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H436),H436/SUM(E436:G436),"")</f>
+        <f aca="false">IF(H436="","",H436/SUM(E436:G436))</f>
         <v>0.0346121201833305</v>
       </c>
       <c r="K436" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H436),SUM(B436:D436)/H436,"")</f>
+        <f aca="false">IF(H436="","",SUM(B436:D436)/H436)</f>
         <v>2.38155958803335</v>
       </c>
     </row>
@@ -19194,11 +19206,11 @@
         <v>0.046308343457303</v>
       </c>
       <c r="J437" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H437),H437/SUM(E437:G437),"")</f>
+        <f aca="false">IF(H437="","",H437/SUM(E437:G437))</f>
         <v>0.0596034016537994</v>
       </c>
       <c r="K437" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H437),SUM(B437:D437)/H437,"")</f>
+        <f aca="false">IF(H437="","",SUM(B437:D437)/H437)</f>
         <v>0.776941284765599</v>
       </c>
     </row>
@@ -19232,11 +19244,11 @@
         <v>0.0377322792080546</v>
       </c>
       <c r="J438" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H438),H438/SUM(E438:G438),"")</f>
+        <f aca="false">IF(H438="","",H438/SUM(E438:G438))</f>
         <v>0.0334346915332117</v>
       </c>
       <c r="K438" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H438),SUM(B438:D438)/H438,"")</f>
+        <f aca="false">IF(H438="","",SUM(B438:D438)/H438)</f>
         <v>1.1285367825384</v>
       </c>
     </row>
@@ -19270,11 +19282,11 @@
         <v>0.0325526396093988</v>
       </c>
       <c r="J439" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H439),H439/SUM(E439:G439),"")</f>
+        <f aca="false">IF(H439="","",H439/SUM(E439:G439))</f>
         <v>0.0303669514800122</v>
       </c>
       <c r="K439" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H439),SUM(B439:D439)/H439,"")</f>
+        <f aca="false">IF(H439="","",SUM(B439:D439)/H439)</f>
         <v>1.07197588242683</v>
       </c>
     </row>
@@ -19308,11 +19320,11 @@
         <v>0.0303013152830915</v>
       </c>
       <c r="J440" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H440),H440/SUM(E440:G440),"")</f>
+        <f aca="false">IF(H440="","",H440/SUM(E440:G440))</f>
         <v>0.0310246077920902</v>
       </c>
       <c r="K440" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H440),SUM(B440:D440)/H440,"")</f>
+        <f aca="false">IF(H440="","",SUM(B440:D440)/H440)</f>
         <v>0.976686489839104</v>
       </c>
     </row>
@@ -19346,11 +19358,11 @@
         <v>0.0125061331298043</v>
       </c>
       <c r="J441" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H441),H441/SUM(E441:G441),"")</f>
+        <f aca="false">IF(H441="","",H441/SUM(E441:G441))</f>
         <v>0.0193098184593578</v>
       </c>
       <c r="K441" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H441),SUM(B441:D441)/H441,"")</f>
+        <f aca="false">IF(H441="","",SUM(B441:D441)/H441)</f>
         <v>0.647656691134952</v>
       </c>
     </row>
@@ -19384,11 +19396,11 @@
         <v>0.0123511516731856</v>
       </c>
       <c r="J442" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H442),H442/SUM(E442:G442),"")</f>
+        <f aca="false">IF(H442="","",H442/SUM(E442:G442))</f>
         <v>0.012090395480226</v>
       </c>
       <c r="K442" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H442),SUM(B442:D442)/H442,"")</f>
+        <f aca="false">IF(H442="","",SUM(B442:D442)/H442)</f>
         <v>1.0215672178289</v>
       </c>
     </row>
@@ -19422,11 +19434,11 @@
         <v>0.0118034948895483</v>
       </c>
       <c r="J443" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H443),H443/SUM(E443:G443),"")</f>
+        <f aca="false">IF(H443="","",H443/SUM(E443:G443))</f>
         <v>0.0134190570392351</v>
       </c>
       <c r="K443" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H443),SUM(B443:D443)/H443,"")</f>
+        <f aca="false">IF(H443="","",SUM(B443:D443)/H443)</f>
         <v>0.87960687960688</v>
       </c>
     </row>
@@ -19460,11 +19472,11 @@
         <v>0.00785984848484849</v>
       </c>
       <c r="J444" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H444),H444/SUM(E444:G444),"")</f>
+        <f aca="false">IF(H444="","",H444/SUM(E444:G444))</f>
         <v>0.0490444214876033</v>
       </c>
       <c r="K444" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H444),SUM(B444:D444)/H444,"")</f>
+        <f aca="false">IF(H444="","",SUM(B444:D444)/H444)</f>
         <v>0.160259785852203</v>
       </c>
     </row>
@@ -19495,11 +19507,11 @@
         <v>0.00773741587626432</v>
       </c>
       <c r="J445" s="473" t="str">
-        <f aca="false">IF(ISNUMBER(H445),H445/SUM(E445:G445),"")</f>
+        <f aca="false">IF(H445="","",H445/SUM(E445:G445))</f>
         <v/>
       </c>
       <c r="K445" s="482" t="str">
-        <f aca="false">IF(ISNUMBER(H445),SUM(B445:D445)/H445,"")</f>
+        <f aca="false">IF(H445="","",SUM(B445:D445)/H445)</f>
         <v/>
       </c>
     </row>
@@ -19533,11 +19545,11 @@
         <v>0.0061114282628485</v>
       </c>
       <c r="J446" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H446),H446/SUM(E446:G446),"")</f>
+        <f aca="false">IF(H446="","",H446/SUM(E446:G446))</f>
         <v>0.0143304583956922</v>
       </c>
       <c r="K446" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H446),SUM(B446:D446)/H446,"")</f>
+        <f aca="false">IF(H446="","",SUM(B446:D446)/H446)</f>
         <v>0.426464254952627</v>
       </c>
     </row>
@@ -19571,11 +19583,11 @@
         <v>0.0028529945553539</v>
       </c>
       <c r="J447" s="473" t="n">
-        <f aca="false">IF(ISNUMBER(H447),H447/SUM(E447:G447),"")</f>
+        <f aca="false">IF(H447="","",H447/SUM(E447:G447))</f>
         <v>0.0196805807622505</v>
       </c>
       <c r="K447" s="482" t="n">
-        <f aca="false">IF(ISNUMBER(H447),SUM(B447:D447)/H447,"")</f>
+        <f aca="false">IF(H447="","",SUM(B447:D447)/H447)</f>
         <v>0.144964957580229</v>
       </c>
     </row>
@@ -19999,12 +20011,12 @@
         <v>1379</v>
       </c>
       <c r="B467" s="472" t="n">
-        <f aca="false">('Cash Flow Statement'!E19+'Cash Flow Statement'!E22)/1000000</f>
+        <f aca="false">SUM('Cash Flow Statement'!E19,'Cash Flow Statement'!E22)/1000000</f>
         <v>1.1979492155</v>
       </c>
       <c r="C467" s="472" t="n">
         <f aca="false">DCF!C10/1000000</f>
-        <v>-4.86489964943638</v>
+        <v>-4.86489964943637</v>
       </c>
       <c r="D467" s="472" t="n">
         <f aca="false">DCF!D10/1000000</f>
@@ -20016,7 +20028,7 @@
       </c>
       <c r="F467" s="472" t="n">
         <f aca="false">DCF!F10/1000000</f>
-        <v>3.62304912114107</v>
+        <v>3.62304912114108</v>
       </c>
       <c r="G467" s="472" t="n">
         <f aca="false">DCF!G10/1000000</f>
@@ -20033,11 +20045,11 @@
       </c>
       <c r="C468" s="472" t="n">
         <f aca="false">DCF!C5/1000000</f>
-        <v>6.7121556766217</v>
+        <v>6.71215567662171</v>
       </c>
       <c r="D468" s="472" t="n">
         <f aca="false">DCF!D5/1000000</f>
-        <v>7.19960685986841</v>
+        <v>7.19960685986843</v>
       </c>
       <c r="E468" s="472" t="n">
         <f aca="false">DCF!E5/1000000</f>
@@ -20062,7 +20074,7 @@
       </c>
       <c r="D469" s="491" t="n">
         <f aca="false">(DCF!D8-DCF!D6+DCF!D7)/DCF!D5</f>
-        <v>6.92278810371681</v>
+        <v>6.9227881037168</v>
       </c>
       <c r="E469" s="491" t="n">
         <f aca="false">(DCF!E8-DCF!E6+DCF!E7)/DCF!E5</f>
@@ -20074,7 +20086,7 @@
       </c>
       <c r="G469" s="491" t="n">
         <f aca="false">(DCF!G8-DCF!G6+DCF!G7)/DCF!G5</f>
-        <v>0.449469686396364</v>
+        <v>0.449469686396365</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20260,27 +20272,27 @@
         <v>1386</v>
       </c>
       <c r="B479" s="472" t="n">
-        <f aca="false">('Balance Sheet'!G48+'Balance Sheet'!G61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!G48,'Balance Sheet'!G61)/1000000</f>
         <v>1.6026</v>
       </c>
       <c r="C479" s="472" t="n">
-        <f aca="false">('Balance Sheet'!H48+'Balance Sheet'!H61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!H48,'Balance Sheet'!H61)/1000000</f>
         <v>1.6026</v>
       </c>
       <c r="D479" s="472" t="n">
-        <f aca="false">('Balance Sheet'!I48+'Balance Sheet'!I61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!I48,'Balance Sheet'!I61)/1000000</f>
         <v>32.7014418323515</v>
       </c>
       <c r="E479" s="472" t="n">
-        <f aca="false">('Balance Sheet'!J48+'Balance Sheet'!J61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!J48,'Balance Sheet'!J61)/1000000</f>
         <v>32.7014418323515</v>
       </c>
       <c r="F479" s="472" t="n">
-        <f aca="false">('Balance Sheet'!K48+'Balance Sheet'!K61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!K48,'Balance Sheet'!K61)/1000000</f>
         <v>26.4816734658812</v>
       </c>
       <c r="G479" s="472" t="n">
-        <f aca="false">('Balance Sheet'!L48+'Balance Sheet'!L61)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!L48,'Balance Sheet'!L61)/1000000</f>
         <v>20.2619050994109</v>
       </c>
     </row>
@@ -20294,7 +20306,7 @@
       </c>
       <c r="C480" s="470" t="n">
         <f aca="false">'Balance Sheet'!H76/1000000</f>
-        <v>74.1621107400675</v>
+        <v>74.1621107400676</v>
       </c>
       <c r="D480" s="470" t="n">
         <f aca="false">'Balance Sheet'!I76/1000000</f>
@@ -20318,27 +20330,27 @@
         <v>1387</v>
       </c>
       <c r="B481" s="491" t="n">
-        <f aca="false">('Balance Sheet'!G48+'Balance Sheet'!G61)/'Balance Sheet'!G76</f>
+        <f aca="false">SUM('Balance Sheet'!G48,'Balance Sheet'!G61)/'Balance Sheet'!G76</f>
         <v>0.0534695345948022</v>
       </c>
       <c r="C481" s="491" t="n">
-        <f aca="false">('Balance Sheet'!H48+'Balance Sheet'!H61)/'Balance Sheet'!H76</f>
+        <f aca="false">SUM('Balance Sheet'!H48,'Balance Sheet'!H61)/'Balance Sheet'!H76</f>
         <v>0.0216094173157637</v>
       </c>
       <c r="D481" s="491" t="n">
-        <f aca="false">('Balance Sheet'!I48+'Balance Sheet'!I61)/'Balance Sheet'!I76</f>
+        <f aca="false">SUM('Balance Sheet'!I48,'Balance Sheet'!I61)/'Balance Sheet'!I76</f>
         <v>0.408821394912379</v>
       </c>
       <c r="E481" s="491" t="n">
-        <f aca="false">('Balance Sheet'!J48+'Balance Sheet'!J61)/'Balance Sheet'!J76</f>
+        <f aca="false">SUM('Balance Sheet'!J48,'Balance Sheet'!J61)/'Balance Sheet'!J76</f>
         <v>0.396922733524847</v>
       </c>
       <c r="F481" s="491" t="n">
-        <f aca="false">('Balance Sheet'!K48+'Balance Sheet'!K61)/'Balance Sheet'!K76</f>
+        <f aca="false">SUM('Balance Sheet'!K48,'Balance Sheet'!K61)/'Balance Sheet'!K76</f>
         <v>0.290695695581815</v>
       </c>
       <c r="G481" s="491" t="n">
-        <f aca="false">('Balance Sheet'!L48+'Balance Sheet'!L61)/'Balance Sheet'!L76</f>
+        <f aca="false">SUM('Balance Sheet'!L48,'Balance Sheet'!L61)/'Balance Sheet'!L76</f>
         <v>0.193058256040505</v>
       </c>
     </row>
@@ -20356,7 +20368,7 @@
       </c>
       <c r="D482" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!G19/1000000</f>
-        <v>7.81749551955852</v>
+        <v>7.81749551955851</v>
       </c>
       <c r="E482" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!H19/1000000</f>
@@ -20451,11 +20463,11 @@
       </c>
       <c r="F485" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!I28/1000000</f>
-        <v>-6.21976836647029</v>
+        <v>-6.2197683664703</v>
       </c>
       <c r="G485" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!J28/1000000</f>
-        <v>-6.21976836647029</v>
+        <v>-6.2197683664703</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20496,27 +20508,27 @@
         <v>1075</v>
       </c>
       <c r="B490" s="473" t="n">
-        <f aca="false">('Income Statement'!D65*(1-Assumption!$D$15))/(Drivers!E100+Drivers!E114)</f>
+        <f aca="false">('Income Statement'!D65*(1-Assumption!$D$15))/SUM(Drivers!E100,Drivers!E114)</f>
         <v>0.12744318375483</v>
       </c>
       <c r="C490" s="473" t="n">
-        <f aca="false">DCF!C5/(Drivers!F100+Drivers!F114)</f>
+        <f aca="false">DCF!C5/SUM(Drivers!F100,Drivers!F114)</f>
         <v>0.16689273549338</v>
       </c>
       <c r="D490" s="473" t="n">
-        <f aca="false">DCF!D5/(Drivers!G100+Drivers!G114)</f>
-        <v>0.0799425729606493</v>
+        <f aca="false">DCF!D5/SUM(Drivers!G100,Drivers!G114)</f>
+        <v>0.0799425729606494</v>
       </c>
       <c r="E490" s="473" t="n">
-        <f aca="false">DCF!E5/(Drivers!H100+Drivers!H114)</f>
+        <f aca="false">DCF!E5/SUM(Drivers!H100,Drivers!H114)</f>
         <v>0.0507708980889596</v>
       </c>
       <c r="F490" s="473" t="n">
-        <f aca="false">DCF!F5/(Drivers!I100+Drivers!I114)</f>
+        <f aca="false">DCF!F5/SUM(Drivers!I100,Drivers!I114)</f>
         <v>0.104296417970394</v>
       </c>
       <c r="G490" s="473" t="n">
-        <f aca="false">DCF!G5/(Drivers!J100+Drivers!J114)</f>
+        <f aca="false">DCF!G5/SUM(Drivers!J100,Drivers!J114)</f>
         <v>0.138811531585547</v>
       </c>
     </row>
@@ -20800,11 +20812,11 @@
       </c>
       <c r="B515" s="470" t="n">
         <f aca="false">DCF!C5/1000000</f>
-        <v>6.7121556766217</v>
+        <v>6.71215567662171</v>
       </c>
       <c r="C515" s="470" t="n">
         <f aca="false">DCF!D5/1000000</f>
-        <v>7.19960685986841</v>
+        <v>7.19960685986843</v>
       </c>
       <c r="D515" s="470" t="n">
         <f aca="false">DCF!E5/1000000</f>
@@ -20850,11 +20862,11 @@
       </c>
       <c r="B517" s="470" t="n">
         <f aca="false">-DCF!C7/1000000</f>
-        <v>-2.58438632806609</v>
+        <v>-2.58438632806608</v>
       </c>
       <c r="C517" s="470" t="n">
         <f aca="false">-DCF!D7/1000000</f>
-        <v>-3.28021567477489</v>
+        <v>-3.2802156747749</v>
       </c>
       <c r="D517" s="470" t="n">
         <f aca="false">-DCF!E7/1000000</f>
@@ -20900,7 +20912,7 @@
       </c>
       <c r="B519" s="470" t="n">
         <f aca="false">DCF!C10/1000000</f>
-        <v>-4.86489964943638</v>
+        <v>-4.86489964943637</v>
       </c>
       <c r="C519" s="470" t="n">
         <f aca="false">DCF!D10/1000000</f>
@@ -20912,7 +20924,7 @@
       </c>
       <c r="E519" s="470" t="n">
         <f aca="false">DCF!F10/1000000</f>
-        <v>3.62304912114107</v>
+        <v>3.62304912114108</v>
       </c>
       <c r="F519" s="470" t="n">
         <f aca="false">DCF!G10/1000000</f>
@@ -20933,23 +20945,23 @@
       </c>
       <c r="C520" s="494" t="n">
         <f aca="false">1/(1+'Discount rate'!$E$5)^2</f>
-        <v>0.77437997144908</v>
+        <v>0.774379971449081</v>
       </c>
       <c r="D520" s="494" t="n">
         <f aca="false">1/(1+'Discount rate'!$E$5)^3</f>
-        <v>0.681445562483728</v>
+        <v>0.681445562483729</v>
       </c>
       <c r="E520" s="494" t="n">
         <f aca="false">1/(1+'Discount rate'!$E$5)^4</f>
-        <v>0.599664340181478</v>
+        <v>0.599664340181479</v>
       </c>
       <c r="F520" s="494" t="n">
         <f aca="false">1/(1+'Discount rate'!$E$5)^5</f>
-        <v>0.527697795220252</v>
+        <v>0.527697795220253</v>
       </c>
       <c r="G520" s="494" t="n">
         <f aca="false">1/(1+'Discount rate'!$E$5)^5</f>
-        <v>0.527697795220252</v>
+        <v>0.527697795220253</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20958,7 +20970,7 @@
       </c>
       <c r="B521" s="472" t="n">
         <f aca="false">DCF!C10/1000000*1/(1+'Discount rate'!$E$5)^1</f>
-        <v>-4.28105632927654</v>
+        <v>-4.28105632927653</v>
       </c>
       <c r="C521" s="472" t="n">
         <f aca="false">DCF!D10/1000000*1/(1+'Discount rate'!$E$5)^2</f>
@@ -20966,7 +20978,7 @@
       </c>
       <c r="D521" s="472" t="n">
         <f aca="false">DCF!E10/1000000*1/(1+'Discount rate'!$E$5)^3</f>
-        <v>-2.50999051366287</v>
+        <v>-2.50999051366288</v>
       </c>
       <c r="E521" s="472" t="n">
         <f aca="false">DCF!F10/1000000*1/(1+'Discount rate'!$E$5)^4</f>
@@ -20978,7 +20990,7 @@
       </c>
       <c r="G521" s="472" t="n">
         <f aca="false">DCF!G12/1000000*1/(1+'Discount rate'!$E$5)^5</f>
-        <v>64.5340734088479</v>
+        <v>64.534073408848</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21014,7 +21026,7 @@
       </c>
       <c r="B527" s="470" t="n">
         <f aca="false">DCF!B28/1000000</f>
-        <v>64.5340734088479</v>
+        <v>64.534073408848</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21050,7 +21062,7 @@
       </c>
       <c r="B531" s="470" t="n">
         <f aca="false">DCF!B33/1000000</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21077,7 +21089,7 @@
       </c>
       <c r="B534" s="490" t="n">
         <f aca="false">DCF!B34</f>
-        <v>4.08894211236575</v>
+        <v>4.08894211236576</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21095,7 +21107,7 @@
       </c>
       <c r="B536" s="490" t="n">
         <f aca="false">DCF!B36</f>
-        <v>4.98450797806063</v>
+        <v>4.98450797806064</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21240,7 +21252,7 @@
       </c>
       <c r="B552" s="471" t="n">
         <f aca="false">VCM!B9</f>
-        <v>0.258614393402926</v>
+        <v>0.258614393402925</v>
       </c>
       <c r="C552" s="471" t="s">
         <v>1454</v>
@@ -21272,7 +21284,7 @@
       </c>
       <c r="B555" s="470" t="n">
         <f aca="false">VCM!E11/1000000</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
       <c r="C555" s="470"/>
     </row>
@@ -21319,7 +21331,7 @@
       </c>
       <c r="B562" s="470" t="n">
         <f aca="false">(VCM!E8-VCM!E6)/1000000</f>
-        <v>-135.782563757076</v>
+        <v>-135.782563757075</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21346,7 +21358,7 @@
       </c>
       <c r="B565" s="470" t="n">
         <f aca="false">VCM!E11/1000000</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21938,7 +21950,7 @@
       </c>
       <c r="B605" s="470" t="n">
         <f aca="false">Summary!B5</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21947,7 +21959,7 @@
       </c>
       <c r="B606" s="470" t="n">
         <f aca="false">Summary!B6</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21965,7 +21977,7 @@
       </c>
       <c r="B608" s="470" t="n">
         <f aca="false">Summary!B8</f>
-        <v>28.779267674012</v>
+        <v>28.7792676740121</v>
       </c>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21974,7 +21986,7 @@
       </c>
       <c r="B609" s="470" t="n">
         <f aca="false">Summary!B10</f>
-        <v>25.6707066753786</v>
+        <v>25.6707066753787</v>
       </c>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22139,7 +22151,7 @@
       </c>
       <c r="B623" s="470" t="n">
         <f aca="false">Summary!B37</f>
-        <v>-38.9101417044817</v>
+        <v>-38.9101417044818</v>
       </c>
       <c r="C623" s="470" t="n">
         <f aca="false">Summary!C37</f>
@@ -22202,7 +22214,7 @@
       </c>
       <c r="B626" s="470" t="n">
         <f aca="false">Summary!B41</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
       <c r="C626" s="470" t="n">
         <f aca="false">Summary!C41</f>
@@ -22223,7 +22235,7 @@
       </c>
       <c r="B627" s="470" t="n">
         <f aca="false">Summary!B42</f>
-        <v>25.2989101339209</v>
+        <v>25.298910133921</v>
       </c>
       <c r="C627" s="470" t="n">
         <f aca="false">Summary!C42</f>
@@ -22244,7 +22256,7 @@
       </c>
       <c r="B628" s="470" t="n">
         <f aca="false">Summary!B43</f>
-        <v>28.779267674012</v>
+        <v>28.7792676740121</v>
       </c>
       <c r="C628" s="470" t="n">
         <f aca="false">Summary!C43</f>
@@ -22963,7 +22975,7 @@
       </c>
       <c r="F662" s="470" t="n">
         <f aca="false">-'Income Statement'!F30/1000000</f>
-        <v>-3.98703100414762</v>
+        <v>-3.98703100414763</v>
       </c>
       <c r="G662" s="470" t="n">
         <f aca="false">-'Income Statement'!G30/1000000</f>
@@ -23074,7 +23086,7 @@
       </c>
       <c r="F665" s="470" t="n">
         <f aca="false">-'Income Statement'!F50/1000000</f>
-        <v>-2.39221860248857</v>
+        <v>-2.39221860248858</v>
       </c>
       <c r="G665" s="470" t="n">
         <f aca="false">-'Income Statement'!G50/1000000</f>
@@ -23086,7 +23098,7 @@
       </c>
       <c r="I665" s="470" t="n">
         <f aca="false">-'Income Statement'!I50/1000000</f>
-        <v>-4.76889694529939</v>
+        <v>-4.7688969452994</v>
       </c>
     </row>
     <row r="666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23148,7 +23160,7 @@
       </c>
       <c r="F667" s="470" t="n">
         <f aca="false">'Income Statement'!F65/1000000</f>
-        <v>8.99950857483553</v>
+        <v>8.99950857483552</v>
       </c>
       <c r="G667" s="470" t="n">
         <f aca="false">'Income Statement'!G65/1000000</f>
@@ -23222,7 +23234,7 @@
       </c>
       <c r="F669" s="470" t="n">
         <f aca="false">'Income Statement'!F76/1000000</f>
-        <v>7.28430648321796</v>
+        <v>7.28430648321795</v>
       </c>
       <c r="G669" s="470" t="n">
         <f aca="false">'Income Statement'!G76/1000000</f>
@@ -23296,7 +23308,7 @@
       </c>
       <c r="F671" s="470" t="n">
         <f aca="false">'Income Statement'!F80/1000000</f>
-        <v>5.82744518657437</v>
+        <v>5.82744518657436</v>
       </c>
       <c r="G671" s="470" t="n">
         <f aca="false">'Income Statement'!G80/1000000</f>
@@ -23651,35 +23663,35 @@
         <v>1524</v>
       </c>
       <c r="B684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!E29+'Balance Sheet'!E30+'Balance Sheet'!E31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!E29:E31)/1000000</f>
         <v>19.794</v>
       </c>
       <c r="C684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!F29+'Balance Sheet'!F30+'Balance Sheet'!F31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!F29:F31)/1000000</f>
         <v>26.0996</v>
       </c>
       <c r="D684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!G29+'Balance Sheet'!G30+'Balance Sheet'!G31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!G29:G31)/1000000</f>
         <v>31.18412</v>
       </c>
       <c r="E684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!H29+'Balance Sheet'!H30+'Balance Sheet'!H31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!H29:H31)/1000000</f>
         <v>43.918883397992</v>
       </c>
       <c r="F684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!I29+'Balance Sheet'!I30+'Balance Sheet'!I31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!I29:I31)/1000000</f>
         <v>95.7502864519111</v>
       </c>
       <c r="G684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!J29+'Balance Sheet'!J30+'Balance Sheet'!J31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!J29:J31)/1000000</f>
         <v>108.998486242234</v>
       </c>
       <c r="H684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!K29+'Balance Sheet'!K30+'Balance Sheet'!K31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!K29:K31)/1000000</f>
         <v>123.158919501079</v>
       </c>
       <c r="I684" s="472" t="n">
-        <f aca="false">('Balance Sheet'!L29+'Balance Sheet'!L30+'Balance Sheet'!L31)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!L29:L31)/1000000</f>
         <v>140.190694305719</v>
       </c>
     </row>
@@ -23984,35 +23996,35 @@
         <v>1526</v>
       </c>
       <c r="B693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!E70+'Balance Sheet'!E72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!E70,'Balance Sheet'!E72)/1000000</f>
         <v>25.144</v>
       </c>
       <c r="C693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!F70+'Balance Sheet'!F72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!F70,'Balance Sheet'!F72)/1000000</f>
         <v>32.144</v>
       </c>
       <c r="D693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!G70+'Balance Sheet'!G72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!G70,'Balance Sheet'!G72)/1000000</f>
         <v>32.144</v>
       </c>
       <c r="E693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!H70+'Balance Sheet'!H72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!H70,'Balance Sheet'!H72)/1000000</f>
         <v>69.7547630979458</v>
       </c>
       <c r="F693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!I70+'Balance Sheet'!I72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!I70,'Balance Sheet'!I72)/1000000</f>
         <v>69.7547630979458</v>
       </c>
       <c r="G693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!J70+'Balance Sheet'!J72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!J70,'Balance Sheet'!J72)/1000000</f>
         <v>69.7547630979458</v>
       </c>
       <c r="H693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!K70+'Balance Sheet'!K72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!K70,'Balance Sheet'!K72)/1000000</f>
         <v>69.7547630979458</v>
       </c>
       <c r="I693" s="472" t="n">
-        <f aca="false">('Balance Sheet'!L70+'Balance Sheet'!L72)/1000000</f>
+        <f aca="false">SUM('Balance Sheet'!L70,'Balance Sheet'!L72)/1000000</f>
         <v>69.7547630979458</v>
       </c>
     </row>
@@ -24046,7 +24058,7 @@
       </c>
       <c r="H694" s="470" t="n">
         <f aca="false">'Balance Sheet'!K75/1000000</f>
-        <v>21.342813743979</v>
+        <v>21.3428137439789</v>
       </c>
       <c r="I694" s="470" t="n">
         <f aca="false">'Balance Sheet'!L75/1000000</f>
@@ -24071,7 +24083,7 @@
       </c>
       <c r="E695" s="470" t="n">
         <f aca="false">'Balance Sheet'!H76/1000000</f>
-        <v>74.1621107400675</v>
+        <v>74.1621107400676</v>
       </c>
       <c r="F695" s="470" t="n">
         <f aca="false">'Balance Sheet'!I76/1000000</f>
@@ -24188,7 +24200,7 @@
       </c>
       <c r="F701" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!G6/1000000</f>
-        <v>5.82744518657437</v>
+        <v>5.82744518657436</v>
       </c>
       <c r="G701" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!H6/1000000</f>
@@ -24299,7 +24311,7 @@
       </c>
       <c r="F704" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!G19/1000000</f>
-        <v>7.81749551955852</v>
+        <v>7.81749551955851</v>
       </c>
       <c r="G704" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!H19/1000000</f>
@@ -24418,11 +24430,11 @@
       </c>
       <c r="H707" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!I28/1000000</f>
-        <v>-6.21976836647029</v>
+        <v>-6.2197683664703</v>
       </c>
       <c r="I707" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!J28/1000000</f>
-        <v>-6.21976836647029</v>
+        <v>-6.2197683664703</v>
       </c>
     </row>
     <row r="708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24455,11 +24467,11 @@
       </c>
       <c r="H708" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!I30/1000000</f>
-        <v>-6.21976836647029</v>
+        <v>-6.2197683664703</v>
       </c>
       <c r="I708" s="470" t="n">
         <f aca="false">'Cash Flow Statement'!J30/1000000</f>
-        <v>-6.21976836647029</v>
+        <v>-6.2197683664703</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24504,20 +24516,20 @@
         <v>1534</v>
       </c>
       <c r="B710" s="472" t="n">
-        <f aca="false">('Cash Flow Statement'!C19+'Cash Flow Statement'!C22)/1000000</f>
+        <f aca="false">SUM('Cash Flow Statement'!C19,'Cash Flow Statement'!C22)/1000000</f>
         <v>-8.9660112</v>
       </c>
       <c r="C710" s="472" t="n">
-        <f aca="false">('Cash Flow Statement'!D19+'Cash Flow Statement'!D22)/1000000</f>
+        <f aca="false">SUM('Cash Flow Statement'!D19,'Cash Flow Statement'!D22)/1000000</f>
         <v>-5.60845625</v>
       </c>
       <c r="D710" s="472" t="n">
-        <f aca="false">('Cash Flow Statement'!E19+'Cash Flow Statement'!E22)/1000000</f>
+        <f aca="false">SUM('Cash Flow Statement'!E19,'Cash Flow Statement'!E22)/1000000</f>
         <v>1.1979492155</v>
       </c>
       <c r="E710" s="472" t="n">
         <f aca="false">DCF!C10/1000000</f>
-        <v>-4.86489964943638</v>
+        <v>-4.86489964943637</v>
       </c>
       <c r="F710" s="472" t="n">
         <f aca="false">DCF!D10/1000000</f>
@@ -24529,7 +24541,7 @@
       </c>
       <c r="H710" s="472" t="n">
         <f aca="false">DCF!F10/1000000</f>
-        <v>3.62304912114107</v>
+        <v>3.62304912114108</v>
       </c>
       <c r="I710" s="472" t="n">
         <f aca="false">DCF!G10/1000000</f>
@@ -25754,7 +25766,7 @@
       </c>
       <c r="B765" s="471" t="n">
         <f aca="false">VCM!B9</f>
-        <v>0.258614393402926</v>
+        <v>0.258614393402925</v>
       </c>
       <c r="C765" s="471" t="str">
         <f aca="false">VCM!C9</f>
@@ -26737,23 +26749,23 @@
       </c>
       <c r="B815" s="470" t="n">
         <f aca="false">Sensitivity!B6</f>
-        <v>52.1978032793631</v>
+        <v>52.1978032793632</v>
       </c>
       <c r="C815" s="470" t="n">
         <f aca="false">Sensitivity!C6</f>
-        <v>55.3308961937083</v>
+        <v>55.3308961937084</v>
       </c>
       <c r="D815" s="470" t="n">
         <f aca="false">Sensitivity!D6</f>
-        <v>59.2111674360915</v>
+        <v>59.2111674360916</v>
       </c>
       <c r="E815" s="470" t="n">
         <f aca="false">Sensitivity!E6</f>
-        <v>64.2362050365185</v>
+        <v>64.2362050365187</v>
       </c>
       <c r="F815" s="470" t="n">
         <f aca="false">Sensitivity!F6</f>
-        <v>71.1465054611667</v>
+        <v>71.1465054611668</v>
       </c>
     </row>
     <row r="816" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26763,7 +26775,7 @@
       </c>
       <c r="B816" s="470" t="n">
         <f aca="false">Sensitivity!B7</f>
-        <v>40.5042160819163</v>
+        <v>40.5042160819164</v>
       </c>
       <c r="C816" s="470" t="n">
         <f aca="false">Sensitivity!C7</f>
@@ -26771,7 +26783,7 @@
       </c>
       <c r="D816" s="470" t="n">
         <f aca="false">Sensitivity!D7</f>
-        <v>44.1310371374378</v>
+        <v>44.1310371374379</v>
       </c>
       <c r="E816" s="470" t="n">
         <f aca="false">Sensitivity!E7</f>
@@ -26793,19 +26805,19 @@
       </c>
       <c r="C817" s="470" t="n">
         <f aca="false">Sensitivity!C8</f>
-        <v>31.9974619633138</v>
+        <v>31.9974619633139</v>
       </c>
       <c r="D817" s="470" t="n">
         <f aca="false">Sensitivity!D8</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
       <c r="E817" s="470" t="n">
         <f aca="false">Sensitivity!E8</f>
-        <v>33.6420774572218</v>
+        <v>33.6420774572219</v>
       </c>
       <c r="F817" s="470" t="n">
         <f aca="false">Sensitivity!F8</f>
-        <v>34.5658654031187</v>
+        <v>34.5658654031188</v>
       </c>
     </row>
     <row r="818" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26845,7 +26857,7 @@
       </c>
       <c r="C819" s="470" t="n">
         <f aca="false">Sensitivity!C10</f>
-        <v>17.4408061810752</v>
+        <v>17.4408061810753</v>
       </c>
       <c r="D819" s="470" t="n">
         <f aca="false">Sensitivity!D10</f>
@@ -26853,7 +26865,7 @@
       </c>
       <c r="E819" s="470" t="n">
         <f aca="false">Sensitivity!E10</f>
-        <v>16.5521135216854</v>
+        <v>16.5521135216855</v>
       </c>
       <c r="F819" s="470" t="n">
         <f aca="false">Sensitivity!F10</f>
@@ -26892,7 +26904,7 @@
       </c>
       <c r="B821" s="470" t="n">
         <f aca="false">Sensitivity!B15</f>
-        <v>13.7654700414121</v>
+        <v>13.765470041412</v>
       </c>
       <c r="C821" s="470" t="n">
         <f aca="false">Sensitivity!C15</f>
@@ -26930,7 +26942,7 @@
       </c>
       <c r="E822" s="470" t="n">
         <f aca="false">Sensitivity!E16</f>
-        <v>40.7642048034216</v>
+        <v>40.7642048034215</v>
       </c>
       <c r="F822" s="470" t="n">
         <f aca="false">Sensitivity!F16</f>
@@ -26970,15 +26982,15 @@
       </c>
       <c r="B824" s="470" t="n">
         <f aca="false">Sensitivity!B18</f>
-        <v>2.75627722583538</v>
+        <v>2.75627722583537</v>
       </c>
       <c r="C824" s="470" t="n">
         <f aca="false">Sensitivity!C18</f>
-        <v>11.4063572952171</v>
+        <v>11.406357295217</v>
       </c>
       <c r="D824" s="470" t="n">
         <f aca="false">Sensitivity!D18</f>
-        <v>20.0564373645988</v>
+        <v>20.0564373645987</v>
       </c>
       <c r="E824" s="470" t="n">
         <f aca="false">Sensitivity!E18</f>
@@ -26996,11 +27008,11 @@
       </c>
       <c r="B825" s="470" t="n">
         <f aca="false">Sensitivity!B19</f>
-        <v>-0.91345371269019</v>
+        <v>-0.913453712690204</v>
       </c>
       <c r="C825" s="470" t="n">
         <f aca="false">Sensitivity!C19</f>
-        <v>6.95025544129316</v>
+        <v>6.95025544129314</v>
       </c>
       <c r="D825" s="470" t="n">
         <f aca="false">Sensitivity!D19</f>
@@ -27008,7 +27020,7 @@
       </c>
       <c r="E825" s="470" t="n">
         <f aca="false">Sensitivity!E19</f>
-        <v>22.6776737492599</v>
+        <v>22.6776737492598</v>
       </c>
       <c r="F825" s="470" t="n">
         <f aca="false">Sensitivity!F19</f>
@@ -27047,23 +27059,23 @@
       </c>
       <c r="B827" s="470" t="n">
         <f aca="false">Sensitivity!B24</f>
-        <v>38.2951839338821</v>
+        <v>38.2951839338822</v>
       </c>
       <c r="C827" s="470" t="n">
         <f aca="false">Sensitivity!C24</f>
-        <v>50.5136094764786</v>
+        <v>50.5136094764787</v>
       </c>
       <c r="D827" s="470" t="n">
         <f aca="false">Sensitivity!D24</f>
-        <v>59.2111674360915</v>
+        <v>59.2111674360916</v>
       </c>
       <c r="E827" s="470" t="n">
         <f aca="false">Sensitivity!E24</f>
-        <v>65.7180638303185</v>
+        <v>65.7180638303186</v>
       </c>
       <c r="F827" s="470" t="n">
         <f aca="false">Sensitivity!F24</f>
-        <v>70.7693725817287</v>
+        <v>70.7693725817288</v>
       </c>
     </row>
     <row r="828" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27077,11 +27089,11 @@
       </c>
       <c r="C828" s="470" t="n">
         <f aca="false">Sensitivity!C25</f>
-        <v>36.9018569043305</v>
+        <v>36.9018569043306</v>
       </c>
       <c r="D828" s="470" t="n">
         <f aca="false">Sensitivity!D25</f>
-        <v>44.1310371374378</v>
+        <v>44.1310371374379</v>
       </c>
       <c r="E828" s="470" t="n">
         <f aca="false">Sensitivity!E25</f>
@@ -27099,23 +27111,23 @@
       </c>
       <c r="B829" s="470" t="n">
         <f aca="false">Sensitivity!B26</f>
-        <v>18.0861659289313</v>
+        <v>18.0861659289314</v>
       </c>
       <c r="C829" s="470" t="n">
         <f aca="false">Sensitivity!C26</f>
-        <v>26.6778646561547</v>
+        <v>26.6778646561548</v>
       </c>
       <c r="D829" s="470" t="n">
         <f aca="false">Sensitivity!D26</f>
-        <v>32.7937752037977</v>
+        <v>32.7937752037978</v>
       </c>
       <c r="E829" s="470" t="n">
         <f aca="false">Sensitivity!E26</f>
-        <v>37.3692659880689</v>
+        <v>37.3692659880691</v>
       </c>
       <c r="F829" s="470" t="n">
         <f aca="false">Sensitivity!F26</f>
-        <v>40.9212230564328</v>
+        <v>40.9212230564329</v>
       </c>
     </row>
     <row r="830" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27141,7 +27153,7 @@
       </c>
       <c r="F830" s="470" t="n">
         <f aca="false">Sensitivity!F27</f>
-        <v>30.9962156491544</v>
+        <v>30.9962156491545</v>
       </c>
     </row>
     <row r="831" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27167,7 +27179,7 @@
       </c>
       <c r="F831" s="470" t="n">
         <f aca="false">Sensitivity!F28</f>
-        <v>23.1378549179401</v>
+        <v>23.1378549179402</v>
       </c>
     </row>
     <row r="832" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27635,7 +27647,7 @@
     <tabColor rgb="FF404040"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -27988,6 +28000,20 @@
       </c>
       <c r="D29" s="499" t="s">
         <v>1668</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="246" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B30" s="246" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C30" s="499" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D30" s="499" t="s">
+        <v>1672</v>
       </c>
     </row>
   </sheetData>
@@ -29466,7 +29492,7 @@
       </c>
       <c r="F30" s="90" t="n">
         <f aca="false">Drivers!G70</f>
-        <v>3987031.00414762</v>
+        <v>3987031.00414763</v>
       </c>
       <c r="G30" s="90" t="n">
         <f aca="false">Drivers!H70</f>
@@ -30161,7 +30187,7 @@
       </c>
       <c r="F50" s="90" t="n">
         <f aca="false">Drivers!G72</f>
-        <v>2392218.60248857</v>
+        <v>2392218.60248858</v>
       </c>
       <c r="G50" s="90" t="n">
         <f aca="false">Drivers!H72</f>
@@ -30173,7 +30199,7 @@
       </c>
       <c r="I50" s="90" t="n">
         <f aca="false">Drivers!J72</f>
-        <v>4768896.94529939</v>
+        <v>4768896.9452994</v>
       </c>
       <c r="J50" s="91"/>
       <c r="K50" s="91"/>
@@ -30220,35 +30246,35 @@
         <v>87</v>
       </c>
       <c r="B52" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,B25:B51)</f>
+        <f aca="false">SUM(B25:B51)</f>
         <v>11437820</v>
       </c>
       <c r="C52" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,C25:C51)</f>
+        <f aca="false">SUM(C25:C51)</f>
         <v>14874838</v>
       </c>
       <c r="D52" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,D25:D51)</f>
+        <f aca="false">SUM(D25:D51)</f>
         <v>19702268.7</v>
       </c>
       <c r="E52" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,E25:E51)</f>
+        <f aca="false">SUM(E25:E51)</f>
         <v>25312536.9719047</v>
       </c>
       <c r="F52" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,F25:F51)</f>
+        <f aca="false">SUM(F25:F51)</f>
         <v>31281148.6466256</v>
       </c>
       <c r="G52" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,G25:G51)</f>
+        <f aca="false">SUM(G25:G51)</f>
         <v>43224542.3362469</v>
       </c>
       <c r="H52" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,H25:H51)</f>
+        <f aca="false">SUM(H25:H51)</f>
         <v>52803207.6332009</v>
       </c>
       <c r="I52" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,I25:I51)</f>
+        <f aca="false">SUM(I25:I51)</f>
         <v>61405286.8498447</v>
       </c>
       <c r="J52" s="102"/>
@@ -30521,35 +30547,35 @@
         <v>95</v>
       </c>
       <c r="B61" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,B55:B60)</f>
+        <f aca="false">SUM(B55:B60)</f>
         <v>0</v>
       </c>
       <c r="C61" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,C55:C60)</f>
+        <f aca="false">SUM(C55:C60)</f>
         <v>0</v>
       </c>
       <c r="D61" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,D55:D60)</f>
+        <f aca="false">SUM(D55:D60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,E55:E60)</f>
+        <f aca="false">SUM(E55:E60)</f>
         <v>0</v>
       </c>
       <c r="F61" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,F55:F60)</f>
+        <f aca="false">SUM(F55:F60)</f>
         <v>0</v>
       </c>
       <c r="G61" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,G55:G60)</f>
+        <f aca="false">SUM(G55:G60)</f>
         <v>0</v>
       </c>
       <c r="H61" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,H55:H60)</f>
+        <f aca="false">SUM(H55:H60)</f>
         <v>0</v>
       </c>
       <c r="I61" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,I55:I60)</f>
+        <f aca="false">SUM(I55:I60)</f>
         <v>0</v>
       </c>
       <c r="J61" s="102"/>
@@ -30579,35 +30605,35 @@
         <v>96</v>
       </c>
       <c r="B63" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,B25:B62)</f>
+        <f aca="false">SUM(B52,B61)</f>
         <v>11437820</v>
       </c>
       <c r="C63" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,C25:C62)</f>
+        <f aca="false">SUM(C52,C61)</f>
         <v>14874838</v>
       </c>
       <c r="D63" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,D25:D62)</f>
+        <f aca="false">SUM(D52,D61)</f>
         <v>19702268.7</v>
       </c>
       <c r="E63" s="100" t="n">
-        <f aca="false">SUBTOTAL(9,E25:E62)</f>
+        <f aca="false">SUM(E52,E61)</f>
         <v>25312536.9719047</v>
       </c>
       <c r="F63" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,F25:F62)</f>
+        <f aca="false">SUM(F52,F61)</f>
         <v>31281148.6466256</v>
       </c>
       <c r="G63" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,G25:G62)</f>
+        <f aca="false">SUM(G52,G61)</f>
         <v>43224542.3362469</v>
       </c>
       <c r="H63" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,H25:H62)</f>
+        <f aca="false">SUM(H52,H61)</f>
         <v>52803207.6332009</v>
       </c>
       <c r="I63" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,I25:I62)</f>
+        <f aca="false">SUM(I52,I61)</f>
         <v>61405286.8498447</v>
       </c>
       <c r="J63" s="102"/>
@@ -30654,7 +30680,7 @@
       </c>
       <c r="F65" s="134" t="n">
         <f aca="false">F21-F63</f>
-        <v>8999508.57483553</v>
+        <v>8999508.57483552</v>
       </c>
       <c r="G65" s="134" t="n">
         <f aca="false">G21-G63</f>
@@ -30928,35 +30954,35 @@
         <v>105</v>
       </c>
       <c r="B74" s="100" t="n">
-        <f aca="false">SUM(B67:B70)+SUM(B72:B73)</f>
+        <f aca="false">SUM(B67:B70,B72:B73)</f>
         <v>114300</v>
       </c>
       <c r="C74" s="100" t="n">
-        <f aca="false">SUM(C67:C70)+SUM(C72:C73)</f>
+        <f aca="false">SUM(C67:C70,C72:C73)</f>
         <v>142560</v>
       </c>
       <c r="D74" s="100" t="n">
-        <f aca="false">SUM(D67:D70)+SUM(D72:D73)</f>
+        <f aca="false">SUM(D67:D70,D72:D73)</f>
         <v>142182</v>
       </c>
       <c r="E74" s="100" t="n">
-        <f aca="false">SUM(E67:E70)+SUM(E72:E73)</f>
+        <f aca="false">SUM(E67:E70,E72:E73)</f>
         <v>160260</v>
       </c>
       <c r="F74" s="101" t="n">
-        <f aca="false">SUM(F67:F70)+SUM(F72:F73)</f>
+        <f aca="false">SUM(F67:F70,F72:F73)</f>
         <v>1715202.09161757</v>
       </c>
       <c r="G74" s="101" t="n">
-        <f aca="false">SUM(G67:G70)+SUM(G72:G73)</f>
+        <f aca="false">SUM(G67:G70,G72:G73)</f>
         <v>3270144.18323515</v>
       </c>
       <c r="H74" s="101" t="n">
-        <f aca="false">SUM(H67:H70)+SUM(H72:H73)</f>
+        <f aca="false">SUM(H67:H70,H72:H73)</f>
         <v>2959155.76491163</v>
       </c>
       <c r="I74" s="101" t="n">
-        <f aca="false">SUM(I67:I70)+SUM(I72:I73)</f>
+        <f aca="false">SUM(I67:I70,I72:I73)</f>
         <v>2337178.9282646</v>
       </c>
       <c r="J74" s="102"/>
@@ -31003,7 +31029,7 @@
       </c>
       <c r="F76" s="134" t="n">
         <f aca="false">F65-F74</f>
-        <v>7284306.48321796</v>
+        <v>7284306.48321795</v>
       </c>
       <c r="G76" s="134" t="n">
         <f aca="false">G65-G74</f>
@@ -31118,7 +31144,7 @@
       </c>
       <c r="F80" s="139" t="n">
         <f aca="false">F76-F78</f>
-        <v>5827445.18657437</v>
+        <v>5827445.18657436</v>
       </c>
       <c r="G80" s="139" t="n">
         <f aca="false">G76-G78</f>
@@ -31159,35 +31185,35 @@
         <v>110</v>
       </c>
       <c r="B82" s="145" t="n">
-        <f aca="false">B65+B71</f>
+        <f aca="false">SUM(B65,B71)</f>
         <v>-2762511.2</v>
       </c>
       <c r="C82" s="145" t="n">
-        <f aca="false">C65+C71</f>
+        <f aca="false">SUM(C65,C71)</f>
         <v>2014563.75</v>
       </c>
       <c r="D82" s="145" t="n">
-        <f aca="false">D65+D71</f>
+        <f aca="false">SUM(D65,D71)</f>
         <v>7694629.2155</v>
       </c>
       <c r="E82" s="146" t="n">
-        <f aca="false">E65+E71</f>
+        <f aca="false">SUM(E65,E71)</f>
         <v>11384204.0346466</v>
       </c>
       <c r="F82" s="145" t="n">
-        <f aca="false">F65+F71</f>
+        <f aca="false">SUM(F65,F71)</f>
         <v>14269774.5825946</v>
       </c>
       <c r="G82" s="145" t="n">
-        <f aca="false">G65+G71</f>
+        <f aca="false">SUM(G65,G71)</f>
         <v>17757514.5630708</v>
       </c>
       <c r="H82" s="145" t="n">
-        <f aca="false">H65+H71</f>
+        <f aca="false">SUM(H65,H71)</f>
         <v>26926664.252477</v>
       </c>
       <c r="I82" s="145" t="n">
-        <f aca="false">I65+I71</f>
+        <f aca="false">SUM(I65,I71)</f>
         <v>34434634.4002363</v>
       </c>
       <c r="J82" s="140"/>
@@ -35135,23 +35161,23 @@
         <v>2933481.76549999</v>
       </c>
       <c r="H7" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,H6)</f>
+        <f aca="false">SUM(H6)</f>
         <v>35546329.4140094</v>
       </c>
       <c r="I7" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,I6)</f>
+        <f aca="false">SUM(I6)</f>
         <v>22631263.7120003</v>
       </c>
       <c r="J7" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,J6)</f>
+        <f aca="false">SUM(J6)</f>
         <v>16331815.9734387</v>
       </c>
       <c r="K7" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,K6)</f>
+        <f aca="false">SUM(K6)</f>
         <v>11367772.1161802</v>
       </c>
       <c r="L7" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,L6)</f>
+        <f aca="false">SUM(L6)</f>
         <v>11935047.6839518</v>
       </c>
       <c r="M7" s="135"/>
@@ -35241,23 +35267,23 @@
         <v>3748500</v>
       </c>
       <c r="H10" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, H9)</f>
+        <f aca="false">SUM(H9)</f>
         <v>4745934.04040822</v>
       </c>
       <c r="I10" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, I9)</f>
+        <f aca="false">SUM(I9)</f>
         <v>5994105.10168572</v>
       </c>
       <c r="J10" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, J9)</f>
+        <f aca="false">SUM(J9)</f>
         <v>9322716.28962655</v>
       </c>
       <c r="K10" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, K9)</f>
+        <f aca="false">SUM(K9)</f>
         <v>11064149.3125862</v>
       </c>
       <c r="L10" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, L9)</f>
+        <f aca="false">SUM(L9)</f>
         <v>12787439.4759941</v>
       </c>
       <c r="M10" s="135"/>
@@ -35348,23 +35374,23 @@
         <v>1767780</v>
       </c>
       <c r="H13" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, H12)</f>
+        <f aca="false">SUM(H12)</f>
         <v>3140078.64608022</v>
       </c>
       <c r="I13" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, I12)</f>
+        <f aca="false">SUM(I12)</f>
         <v>4806283.95020536</v>
       </c>
       <c r="J13" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, J12)</f>
+        <f aca="false">SUM(J12)</f>
         <v>7864228.18603618</v>
       </c>
       <c r="K13" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, K12)</f>
+        <f aca="false">SUM(K12)</f>
         <v>11638712.267544</v>
       </c>
       <c r="L13" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, L12)</f>
+        <f aca="false">SUM(L12)</f>
         <v>13998719.0175129</v>
       </c>
       <c r="M13" s="135"/>
@@ -35611,23 +35637,23 @@
         <v>2073090</v>
       </c>
       <c r="H20" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,H15:H19)</f>
+        <f aca="false">SUM(H15:H19)</f>
         <v>2546952.6795984</v>
       </c>
       <c r="I20" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,I15:I19)</f>
+        <f aca="false">SUM(I15:I19)</f>
         <v>3189624.8033181</v>
       </c>
       <c r="J20" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,J15:J19)</f>
+        <f aca="false">SUM(J15:J19)</f>
         <v>4416066.59677417</v>
       </c>
       <c r="K20" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,K15:K19)</f>
+        <f aca="false">SUM(K15:K19)</f>
         <v>5664173.30353806</v>
       </c>
       <c r="L20" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,L15:L19)</f>
+        <f aca="false">SUM(L15:L19)</f>
         <v>6812709.92185628</v>
       </c>
       <c r="M20" s="135"/>
@@ -35672,23 +35698,23 @@
         <v>10522851.7655</v>
       </c>
       <c r="H22" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,H5:H21)</f>
+        <f aca="false">SUM(H7,H10,H13,H20)</f>
         <v>45979294.7800963</v>
       </c>
       <c r="I22" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,I5:I21)</f>
+        <f aca="false">SUM(I7,I10,I13,I20)</f>
         <v>36621277.5672095</v>
       </c>
       <c r="J22" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,J5:J21)</f>
+        <f aca="false">SUM(J7,J10,J13,J20)</f>
         <v>37934827.0458756</v>
       </c>
       <c r="K22" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,K5:K21)</f>
+        <f aca="false">SUM(K7,K10,K13,K20)</f>
         <v>39734806.9998484</v>
       </c>
       <c r="L22" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,L5:L21)</f>
+        <f aca="false">SUM(L7,L10,L13,L20)</f>
         <v>45533916.0993151</v>
       </c>
       <c r="M22" s="102"/>
@@ -35780,23 +35806,23 @@
         <v>9789432</v>
       </c>
       <c r="H26" s="110" t="n">
-        <f aca="false">G26+'Income Statement'!E71</f>
+        <f aca="false">SUM(G26,'Income Statement'!E71)</f>
         <v>13531526.4</v>
       </c>
       <c r="I26" s="110" t="n">
-        <f aca="false">H26+'Income Statement'!F71</f>
+        <f aca="false">SUM(H26,'Income Statement'!F71)</f>
         <v>18801792.407759</v>
       </c>
       <c r="J26" s="110" t="n">
-        <f aca="false">I26+'Income Statement'!G71</f>
+        <f aca="false">SUM(I26,'Income Statement'!G71)</f>
         <v>30291826.7819884</v>
       </c>
       <c r="K26" s="110" t="n">
-        <f aca="false">J26+'Income Statement'!H71</f>
+        <f aca="false">SUM(J26,'Income Statement'!H71)</f>
         <v>43371645.1310564</v>
       </c>
       <c r="L26" s="110" t="n">
-        <f aca="false">K26+'Income Statement'!I71</f>
+        <f aca="false">SUM(K26,'Income Statement'!I71)</f>
         <v>58150715.4711859</v>
       </c>
       <c r="M26" s="97"/>
@@ -35823,23 +35849,23 @@
         <v>0</v>
       </c>
       <c r="H27" s="110" t="n">
-        <f aca="false">G27+'Income Statement'!E72</f>
+        <f aca="false">SUM(G27,'Income Statement'!E72)</f>
         <v>0</v>
       </c>
       <c r="I27" s="110" t="n">
-        <f aca="false">H27+'Income Statement'!F72</f>
+        <f aca="false">SUM(H27,'Income Statement'!F72)</f>
         <v>0</v>
       </c>
       <c r="J27" s="110" t="n">
-        <f aca="false">I27+'Income Statement'!G72</f>
+        <f aca="false">SUM(I27,'Income Statement'!G72)</f>
         <v>0</v>
       </c>
       <c r="K27" s="110" t="n">
-        <f aca="false">J27+'Income Statement'!H72</f>
+        <f aca="false">SUM(J27,'Income Statement'!H72)</f>
         <v>0</v>
       </c>
       <c r="L27" s="110" t="n">
-        <f aca="false">K27+'Income Statement'!I72</f>
+        <f aca="false">SUM(K27,'Income Statement'!I72)</f>
         <v>0</v>
       </c>
       <c r="M27" s="97"/>
@@ -35929,23 +35955,23 @@
         <v>21633696</v>
       </c>
       <c r="H30" s="89" t="n">
-        <f aca="false">G30+Drivers!F95</f>
+        <f aca="false">SUM(G30,Drivers!F95)</f>
         <v>34368459.397992</v>
       </c>
       <c r="I30" s="89" t="n">
-        <f aca="false">H30+Drivers!G95</f>
+        <f aca="false">SUM(H30,Drivers!G95)</f>
         <v>86199862.4519111</v>
       </c>
       <c r="J30" s="89" t="n">
-        <f aca="false">I30+Drivers!H95</f>
+        <f aca="false">SUM(I30,Drivers!H95)</f>
         <v>99448062.2422336</v>
       </c>
       <c r="K30" s="89" t="n">
-        <f aca="false">J30+Drivers!I95</f>
+        <f aca="false">SUM(J30,Drivers!I95)</f>
         <v>113608495.501079</v>
       </c>
       <c r="L30" s="89" t="n">
-        <f aca="false">K30+Drivers!J95</f>
+        <f aca="false">SUM(K30,Drivers!J95)</f>
         <v>130640270.305719</v>
       </c>
       <c r="M30" s="94"/>
@@ -36074,23 +36100,23 @@
         <v>31917539.7655</v>
       </c>
       <c r="H34" s="179" t="n">
-        <f aca="false">H22+H32</f>
+        <f aca="false">SUM(H22,H32)</f>
         <v>76366651.7780883</v>
       </c>
       <c r="I34" s="179" t="n">
-        <f aca="false">I22+I32</f>
+        <f aca="false">SUM(I22,I32)</f>
         <v>113569771.611362</v>
       </c>
       <c r="J34" s="179" t="n">
-        <f aca="false">J22+J32</f>
+        <f aca="false">SUM(J22,J32)</f>
         <v>116641486.506121</v>
       </c>
       <c r="K34" s="179" t="n">
-        <f aca="false">K22+K32</f>
+        <f aca="false">SUM(K22,K32)</f>
         <v>119522081.369871</v>
       </c>
       <c r="L34" s="179" t="n">
-        <f aca="false">L22+L32</f>
+        <f aca="false">SUM(L22,L32)</f>
         <v>127573894.933849</v>
       </c>
       <c r="M34" s="180"/>
@@ -36264,23 +36290,23 @@
         <v>263640</v>
       </c>
       <c r="H41" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, H40)</f>
+        <f aca="false">SUM(H40)</f>
         <v>474593.404040822</v>
       </c>
       <c r="I41" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, I40)</f>
+        <f aca="false">SUM(I40)</f>
         <v>719292.612202287</v>
       </c>
       <c r="J41" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, J40)</f>
+        <f aca="false">SUM(J40)</f>
         <v>1331816.61280379</v>
       </c>
       <c r="K41" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, K40)</f>
+        <f aca="false">SUM(K40)</f>
         <v>1659622.39688793</v>
       </c>
       <c r="L41" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, L40)</f>
+        <f aca="false">SUM(L40)</f>
         <v>2019069.39094643</v>
       </c>
       <c r="M41" s="135"/>
@@ -36399,23 +36425,23 @@
         <v>0</v>
       </c>
       <c r="H45" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,H43:H44)</f>
+        <f aca="false">SUM(H43:H44)</f>
         <v>0</v>
       </c>
       <c r="I45" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,I43:I44)</f>
+        <f aca="false">SUM(I43:I44)</f>
         <v>0</v>
       </c>
       <c r="J45" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,J43:J44)</f>
+        <f aca="false">SUM(J43:J44)</f>
         <v>0</v>
       </c>
       <c r="K45" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,K43:K44)</f>
+        <f aca="false">SUM(K43:K44)</f>
         <v>0</v>
       </c>
       <c r="L45" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,L43:L44)</f>
+        <f aca="false">SUM(L43:L44)</f>
         <v>0</v>
       </c>
       <c r="M45" s="135"/>
@@ -36504,23 +36530,23 @@
         <v>102600</v>
       </c>
       <c r="H48" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,H47:H47)</f>
+        <f aca="false">SUM(H47:H47)</f>
         <v>102600</v>
       </c>
       <c r="I48" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,I47:I47)</f>
+        <f aca="false">SUM(I47:I47)</f>
         <v>102600</v>
       </c>
       <c r="J48" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,J47:J47)</f>
+        <f aca="false">SUM(J47:J47)</f>
         <v>102600</v>
       </c>
       <c r="K48" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,K47:K47)</f>
+        <f aca="false">SUM(K47:K47)</f>
         <v>102600</v>
       </c>
       <c r="L48" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,L47:L47)</f>
+        <f aca="false">SUM(L47:L47)</f>
         <v>102600</v>
       </c>
       <c r="M48" s="135"/>
@@ -36602,23 +36628,23 @@
         <v>0</v>
       </c>
       <c r="H51" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, H50)</f>
+        <f aca="false">SUM(H50)</f>
         <v>0</v>
       </c>
       <c r="I51" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, I50)</f>
+        <f aca="false">SUM(I50)</f>
         <v>0</v>
       </c>
       <c r="J51" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, J50)</f>
+        <f aca="false">SUM(J50)</f>
         <v>0</v>
       </c>
       <c r="K51" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, K50)</f>
+        <f aca="false">SUM(K50)</f>
         <v>0</v>
       </c>
       <c r="L51" s="171" t="n">
-        <f aca="false">SUBTOTAL(9, L50)</f>
+        <f aca="false">SUM(L50)</f>
         <v>0</v>
       </c>
       <c r="M51" s="135"/>
@@ -36779,23 +36805,23 @@
         <v>79092</v>
       </c>
       <c r="H56" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,H53:H55)</f>
+        <f aca="false">SUM(H53:H55)</f>
         <v>127347.63397992</v>
       </c>
       <c r="I56" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,I53:I55)</f>
+        <f aca="false">SUM(I53:I55)</f>
         <v>159481.240165905</v>
       </c>
       <c r="J56" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,J53:J55)</f>
+        <f aca="false">SUM(J53:J55)</f>
         <v>220803.329838708</v>
       </c>
       <c r="K56" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,K53:K55)</f>
+        <f aca="false">SUM(K53:K55)</f>
         <v>283208.665176903</v>
       </c>
       <c r="L56" s="171" t="n">
-        <f aca="false">SUBTOTAL(9,L53:L55)</f>
+        <f aca="false">SUM(L53:L55)</f>
         <v>340635.496092814</v>
       </c>
       <c r="M56" s="135"/>
@@ -36836,23 +36862,23 @@
         <v>445332</v>
       </c>
       <c r="H58" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,H40:H56)</f>
+        <f aca="false">SUM(H41,H45,H48,H51,H56)</f>
         <v>704541.038020742</v>
       </c>
       <c r="I58" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,I40:I56)</f>
+        <f aca="false">SUM(I41,I45,I48,I51,I56)</f>
         <v>981373.852368192</v>
       </c>
       <c r="J58" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,J40:J56)</f>
+        <f aca="false">SUM(J41,J45,J48,J51,J56)</f>
         <v>1655219.9426425</v>
       </c>
       <c r="K58" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,K40:K56)</f>
+        <f aca="false">SUM(K41,K45,K48,K51,K56)</f>
         <v>2045431.06206483</v>
       </c>
       <c r="L58" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,L40:L56)</f>
+        <f aca="false">SUM(L41,L45,L48,L51,L56)</f>
         <v>2462304.88703925</v>
       </c>
       <c r="M58" s="102"/>
@@ -37041,23 +37067,23 @@
         <v>1500000</v>
       </c>
       <c r="H64" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,H61:H63)</f>
+        <f aca="false">SUM(H61:H63)</f>
         <v>1500000</v>
       </c>
       <c r="I64" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,I61:I63)</f>
+        <f aca="false">SUM(I61:I63)</f>
         <v>32598841.8323515</v>
       </c>
       <c r="J64" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,J61:J63)</f>
+        <f aca="false">SUM(J61:J63)</f>
         <v>32598841.8323515</v>
       </c>
       <c r="K64" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,K61:K63)</f>
+        <f aca="false">SUM(K61:K63)</f>
         <v>26379073.4658812</v>
       </c>
       <c r="L64" s="101" t="n">
-        <f aca="false">SUBTOTAL(9,L61:L63)</f>
+        <f aca="false">SUM(L61:L63)</f>
         <v>20159305.0994109</v>
       </c>
       <c r="M64" s="102"/>
@@ -37098,23 +37124,23 @@
         <v>1945332</v>
       </c>
       <c r="H66" s="190" t="n">
-        <f aca="false">H58+H64</f>
+        <f aca="false">SUM(H58,H64)</f>
         <v>2204541.03802074</v>
       </c>
       <c r="I66" s="190" t="n">
-        <f aca="false">I58+I64</f>
+        <f aca="false">SUM(I58,I64)</f>
         <v>33580215.6847197</v>
       </c>
       <c r="J66" s="190" t="n">
-        <f aca="false">J58+J64</f>
+        <f aca="false">SUM(J58,J64)</f>
         <v>34254061.774994</v>
       </c>
       <c r="K66" s="190" t="n">
-        <f aca="false">K58+K64</f>
+        <f aca="false">SUM(K58,K64)</f>
         <v>28424504.527946</v>
       </c>
       <c r="L66" s="190" t="n">
-        <f aca="false">L58+L64</f>
+        <f aca="false">SUM(L58,L64)</f>
         <v>22621609.9864501</v>
       </c>
       <c r="M66" s="180"/>
@@ -37221,23 +37247,23 @@
         <v>32144000</v>
       </c>
       <c r="H70" s="90" t="n">
-        <f aca="false">G70+G72</f>
+        <f aca="false">SUM(G70,G72)</f>
         <v>32144000</v>
       </c>
       <c r="I70" s="90" t="n">
-        <f aca="false">H70+H72</f>
+        <f aca="false">SUM(H70,H72)</f>
         <v>69754763.0979458</v>
       </c>
       <c r="J70" s="90" t="n">
-        <f aca="false">I70+I72</f>
+        <f aca="false">SUM(I70,I72)</f>
         <v>69754763.0979458</v>
       </c>
       <c r="K70" s="90" t="n">
-        <f aca="false">J70+J72</f>
+        <f aca="false">SUM(J70,J72)</f>
         <v>69754763.0979458</v>
       </c>
       <c r="L70" s="90" t="n">
-        <f aca="false">K70+K72</f>
+        <f aca="false">SUM(K70,K72)</f>
         <v>69754763.0979458</v>
       </c>
       <c r="M70" s="91"/>
@@ -37420,23 +37446,23 @@
         <v>-2171792.2345</v>
       </c>
       <c r="H75" s="110" t="n">
-        <f aca="false">'Income Statement'!E80+G75</f>
+        <f aca="false">SUM('Income Statement'!E80,G75)</f>
         <v>4407347.64212171</v>
       </c>
       <c r="I75" s="110" t="n">
-        <f aca="false">'Income Statement'!F80+H75</f>
+        <f aca="false">SUM('Income Statement'!F80,H75)</f>
         <v>10234792.8286961</v>
       </c>
       <c r="J75" s="110" t="n">
-        <f aca="false">'Income Statement'!G80+I75</f>
+        <f aca="false">SUM('Income Statement'!G80,I75)</f>
         <v>12632661.6331811</v>
       </c>
       <c r="K75" s="110" t="n">
-        <f aca="false">'Income Statement'!H80+J75</f>
-        <v>21342813.743979</v>
+        <f aca="false">SUM('Income Statement'!H80,J75)</f>
+        <v>21342813.7439789</v>
       </c>
       <c r="L75" s="110" t="n">
-        <f aca="false">'Income Statement'!I80+K75</f>
+        <f aca="false">SUM('Income Statement'!I80,K75)</f>
         <v>35197521.8494527</v>
       </c>
       <c r="M75" s="97"/>
@@ -37524,23 +37550,23 @@
         <v>31917539.7655</v>
       </c>
       <c r="H78" s="179" t="n">
-        <f aca="false">H66+H76</f>
+        <f aca="false">SUM(H66,H76)</f>
         <v>76366651.7780883</v>
       </c>
       <c r="I78" s="179" t="n">
-        <f aca="false">I66+I76</f>
+        <f aca="false">SUM(I66,I76)</f>
         <v>113569771.611362</v>
       </c>
       <c r="J78" s="179" t="n">
-        <f aca="false">J66+J76</f>
+        <f aca="false">SUM(J66,J76)</f>
         <v>116641486.506121</v>
       </c>
       <c r="K78" s="179" t="n">
-        <f aca="false">K66+K76</f>
+        <f aca="false">SUM(K66,K76)</f>
         <v>119522081.369871</v>
       </c>
       <c r="L78" s="179" t="n">
-        <f aca="false">L66+L76</f>
+        <f aca="false">SUM(L66,L76)</f>
         <v>127573894.933849</v>
       </c>
       <c r="M78" s="180"/>
@@ -38725,7 +38751,7 @@
       </c>
       <c r="G6" s="110" t="n">
         <f aca="false">'Income Statement'!F80</f>
-        <v>5827445.18657437</v>
+        <v>5827445.18657436</v>
       </c>
       <c r="H6" s="110" t="n">
         <f aca="false">'Income Statement'!G80</f>
@@ -38994,7 +39020,7 @@
       </c>
       <c r="J15" s="110" t="n">
         <f aca="false">'Balance Sheet'!L41-'Balance Sheet'!K41</f>
-        <v>359446.994058503</v>
+        <v>359446.994058504</v>
       </c>
       <c r="K15" s="97"/>
       <c r="L15" s="97"/>
@@ -39065,7 +39091,7 @@
       </c>
       <c r="H17" s="110" t="n">
         <f aca="false">('Balance Sheet'!J56-'Balance Sheet'!I56)+('Balance Sheet'!J51-'Balance Sheet'!I51)</f>
-        <v>61322.0896728033</v>
+        <v>61322.0896728032</v>
       </c>
       <c r="I17" s="110" t="n">
         <f aca="false">('Balance Sheet'!K56-'Balance Sheet'!J56)+('Balance Sheet'!K51-'Balance Sheet'!J51)</f>
@@ -39114,7 +39140,7 @@
       </c>
       <c r="G19" s="211" t="n">
         <f aca="false">SUM(G6:G18)</f>
-        <v>7817495.51955852</v>
+        <v>7817495.51955851</v>
       </c>
       <c r="H19" s="211" t="n">
         <f aca="false">SUM(H6:H18)</f>
@@ -39354,11 +39380,11 @@
       </c>
       <c r="I28" s="109" t="n">
         <f aca="false">('Balance Sheet'!K61-'Balance Sheet'!J61)</f>
-        <v>-6219768.36647029</v>
+        <v>-6219768.3664703</v>
       </c>
       <c r="J28" s="109" t="n">
         <f aca="false">('Balance Sheet'!L61-'Balance Sheet'!K61)</f>
-        <v>-6219768.36647029</v>
+        <v>-6219768.3664703</v>
       </c>
       <c r="K28" s="96"/>
       <c r="L28" s="96"/>
@@ -39407,11 +39433,11 @@
       </c>
       <c r="I30" s="211" t="n">
         <f aca="false">SUM(I27:I29)</f>
-        <v>-6219768.36647029</v>
+        <v>-6219768.3664703</v>
       </c>
       <c r="J30" s="211" t="n">
         <f aca="false">SUM(J27:J29)</f>
-        <v>-6219768.36647029</v>
+        <v>-6219768.3664703</v>
       </c>
       <c r="K30" s="129"/>
       <c r="L30" s="129"/>
@@ -39502,24 +39528,24 @@
         <v>1197949.21549999</v>
       </c>
       <c r="F34" s="213" t="n">
-        <f aca="false">F19+F24+F30</f>
-        <v>32612847.6485094</v>
+        <f aca="false">SUM(F19,F24,F30)</f>
+        <v>32612847.6485095</v>
       </c>
       <c r="G34" s="213" t="n">
-        <f aca="false">G19+G24+G30</f>
+        <f aca="false">SUM(G19,G24,G30)</f>
         <v>-12915065.7020091</v>
       </c>
       <c r="H34" s="213" t="n">
-        <f aca="false">H19+H24+H30</f>
+        <f aca="false">SUM(H19,H24,H30)</f>
         <v>-6299447.73856156</v>
       </c>
       <c r="I34" s="213" t="n">
-        <f aca="false">I19+I24+I30</f>
-        <v>-4964043.85725851</v>
+        <f aca="false">SUM(I19,I24,I30)</f>
+        <v>-4964043.85725852</v>
       </c>
       <c r="J34" s="213" t="n">
-        <f aca="false">J19+J24+J30</f>
-        <v>567275.567771617</v>
+        <f aca="false">SUM(J19,J24,J30)</f>
+        <v>567275.567771595</v>
       </c>
       <c r="K34" s="129"/>
       <c r="L34" s="129"/>
@@ -39557,23 +39583,23 @@
         <v>2933481.76549999</v>
       </c>
       <c r="F36" s="211" t="n">
-        <f aca="false">F34+F32</f>
+        <f aca="false">SUM(F34,F32)</f>
         <v>35546329.4140094</v>
       </c>
       <c r="G36" s="211" t="n">
-        <f aca="false">G34+G32</f>
+        <f aca="false">SUM(G34,G32)</f>
         <v>22631263.7120003</v>
       </c>
       <c r="H36" s="211" t="n">
-        <f aca="false">H34+H32</f>
+        <f aca="false">SUM(H34,H32)</f>
         <v>16331815.9734387</v>
       </c>
       <c r="I36" s="211" t="n">
-        <f aca="false">I34+I32</f>
+        <f aca="false">SUM(I34,I32)</f>
         <v>11367772.1161802</v>
       </c>
       <c r="J36" s="211" t="n">
-        <f aca="false">J34+J32</f>
+        <f aca="false">SUM(J34,J32)</f>
         <v>11935047.6839518</v>
       </c>
       <c r="K36" s="129"/>
@@ -41760,7 +41786,7 @@
         <v>163</v>
       </c>
       <c r="B8" s="226" t="n">
-        <f aca="false">'Balance Sheet'!I61+'Balance Sheet'!I48</f>
+        <f aca="false">SUM('Balance Sheet'!I61,'Balance Sheet'!I48)</f>
         <v>32701441.8323515</v>
       </c>
       <c r="C8" s="224"/>
@@ -41774,7 +41800,7 @@
         <v>208</v>
       </c>
       <c r="B9" s="226" t="n">
-        <f aca="false">B7+B8</f>
+        <f aca="false">SUM(B7:B8)</f>
         <v>112690997.758993</v>
       </c>
       <c r="C9" s="224"/>
@@ -41847,7 +41873,7 @@
         <v>219</v>
       </c>
       <c r="B17" s="235" t="n">
-        <f aca="false">B14+B16</f>
+        <f aca="false">SUM(B14,B16)</f>
         <v>0.0813</v>
       </c>
     </row>
@@ -41920,7 +41946,7 @@
         <v>230</v>
       </c>
       <c r="B24" s="235" t="n">
-        <f aca="false">B13+B17</f>
+        <f aca="false">SUM(B13,B17)</f>
         <v>0.120507</v>
       </c>
     </row>
@@ -42204,7 +42230,7 @@
       </c>
       <c r="F4" s="256" t="n">
         <f aca="false">Drivers!G40</f>
-        <v>0.252329824918865</v>
+        <v>0.252329824918866</v>
       </c>
       <c r="G4" s="256" t="n">
         <f aca="false">Drivers!H40</f>
@@ -42247,7 +42273,7 @@
       </c>
       <c r="I5" s="257" t="n">
         <f aca="false">Drivers!J83</f>
-        <v>0.524061045664692</v>
+        <v>0.524061045664691</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42323,23 +42349,23 @@
         <v>0.159619856659944</v>
       </c>
       <c r="E8" s="257" t="n">
-        <f aca="false">(Drivers!F105+Drivers!F107+Drivers!F109)/Drivers!F39</f>
+        <f aca="false">SUM(Drivers!F105,Drivers!F107,Drivers!F109)/Drivers!F39</f>
         <v>0.163850164153531</v>
       </c>
       <c r="F8" s="257" t="n">
-        <f aca="false">(Drivers!G105+Drivers!G107+Drivers!G109)/Drivers!G39</f>
+        <f aca="false">SUM(Drivers!G105,Drivers!G107,Drivers!G109)/Drivers!G39</f>
         <v>0.175444006337744</v>
       </c>
       <c r="G8" s="257" t="n">
-        <f aca="false">(Drivers!H105+Drivers!H107+Drivers!H109)/Drivers!H39</f>
+        <f aca="false">SUM(Drivers!H105,Drivers!H107,Drivers!H109)/Drivers!H39</f>
         <v>0.195676497163493</v>
       </c>
       <c r="H8" s="257" t="n">
-        <f aca="false">(Drivers!I105+Drivers!I107+Drivers!I109)/Drivers!I39</f>
+        <f aca="false">SUM(Drivers!I105,Drivers!I107,Drivers!I109)/Drivers!I39</f>
         <v>0.200326037806429</v>
       </c>
       <c r="I8" s="257" t="n">
-        <f aca="false">(Drivers!J105+Drivers!J107+Drivers!J109)/Drivers!J39</f>
+        <f aca="false">SUM(Drivers!J105,Drivers!J107,Drivers!J109)/Drivers!J39</f>
         <v>0.197271680730586</v>
       </c>
     </row>
@@ -42354,23 +42380,23 @@
         <v>0.00720834966707064</v>
       </c>
       <c r="E9" s="257" t="n">
-        <f aca="false">(Drivers!F111+Drivers!F113)/Drivers!F39</f>
+        <f aca="false">SUM(Drivers!F111,Drivers!F113)/Drivers!F39</f>
         <v>0.00945350956603803</v>
       </c>
       <c r="F9" s="257" t="n">
-        <f aca="false">(Drivers!G111+Drivers!G113)/Drivers!G39</f>
+        <f aca="false">SUM(Drivers!G111,Drivers!G113)/Drivers!G39</f>
         <v>0.0110204040482005</v>
       </c>
       <c r="G9" s="257" t="n">
-        <f aca="false">(Drivers!H111+Drivers!H113)/Drivers!H39</f>
+        <f aca="false">SUM(Drivers!H111,Drivers!H113)/Drivers!H39</f>
         <v>0.0140633743501663</v>
       </c>
       <c r="H9" s="257" t="n">
-        <f aca="false">(Drivers!I111+Drivers!I113)/Drivers!I39</f>
+        <f aca="false">SUM(Drivers!I111,Drivers!I113)/Drivers!I39</f>
         <v>0.0137201385476766</v>
       </c>
       <c r="I9" s="257" t="n">
-        <f aca="false">(Drivers!J111+Drivers!J113)/Drivers!J39</f>
+        <f aca="false">SUM(Drivers!J111,Drivers!J113)/Drivers!J39</f>
         <v>0.0138547210382108</v>
       </c>
     </row>
@@ -42385,23 +42411,23 @@
         <v>0.493914514643507</v>
       </c>
       <c r="E10" s="257" t="n">
-        <f aca="false">Drivers!F105/(Drivers!F105+Drivers!F107+Drivers!F109)</f>
+        <f aca="false">Drivers!F105/SUM(Drivers!F105,Drivers!F107,Drivers!F109)</f>
         <v>0.454897900441158</v>
       </c>
       <c r="F10" s="257" t="n">
-        <f aca="false">Drivers!G105/(Drivers!G105+Drivers!G107+Drivers!G109)</f>
+        <f aca="false">Drivers!G105/SUM(Drivers!G105,Drivers!G107,Drivers!G109)</f>
         <v>0.428455980367297</v>
       </c>
       <c r="G10" s="257" t="n">
-        <f aca="false">Drivers!H105/(Drivers!H105+Drivers!H107+Drivers!H109)</f>
-        <v>0.431547077320223</v>
+        <f aca="false">Drivers!H105/SUM(Drivers!H105,Drivers!H107,Drivers!H109)</f>
+        <v>0.431547077320222</v>
       </c>
       <c r="H10" s="257" t="n">
-        <f aca="false">Drivers!I105/(Drivers!I105+Drivers!I107+Drivers!I109)</f>
+        <f aca="false">Drivers!I105/SUM(Drivers!I105,Drivers!I107,Drivers!I109)</f>
         <v>0.390035453404267</v>
       </c>
       <c r="I10" s="257" t="n">
-        <f aca="false">Drivers!J105/(Drivers!J105+Drivers!J107+Drivers!J109)</f>
+        <f aca="false">Drivers!J105/SUM(Drivers!J105,Drivers!J107,Drivers!J109)</f>
         <v>0.380591373432891</v>
       </c>
     </row>
@@ -42416,23 +42442,23 @@
         <v>0.232928424889022</v>
       </c>
       <c r="E11" s="257" t="n">
-        <f aca="false">Drivers!F107/(Drivers!F105+Drivers!F107+Drivers!F109)</f>
+        <f aca="false">Drivers!F107/SUM(Drivers!F105,Drivers!F107,Drivers!F109)</f>
         <v>0.300976619388318</v>
       </c>
       <c r="F11" s="257" t="n">
-        <f aca="false">Drivers!G107/(Drivers!G105+Drivers!G107+Drivers!G109)</f>
+        <f aca="false">Drivers!G107/SUM(Drivers!G105,Drivers!G107,Drivers!G109)</f>
         <v>0.343551050052444</v>
       </c>
       <c r="G11" s="257" t="n">
-        <f aca="false">Drivers!H107/(Drivers!H105+Drivers!H107+Drivers!H109)</f>
+        <f aca="false">Drivers!H107/SUM(Drivers!H105,Drivers!H107,Drivers!H109)</f>
         <v>0.364033891371286</v>
       </c>
       <c r="H11" s="257" t="n">
-        <f aca="false">Drivers!I107/(Drivers!I105+Drivers!I107+Drivers!I109)</f>
+        <f aca="false">Drivers!I107/SUM(Drivers!I105,Drivers!I107,Drivers!I109)</f>
         <v>0.410290053763946</v>
       </c>
       <c r="I11" s="257" t="n">
-        <f aca="false">Drivers!J107/(Drivers!J105+Drivers!J107+Drivers!J109)</f>
+        <f aca="false">Drivers!J107/SUM(Drivers!J105,Drivers!J107,Drivers!J109)</f>
         <v>0.416642573924064</v>
       </c>
     </row>
@@ -42447,23 +42473,23 @@
         <v>0.769230769230769</v>
       </c>
       <c r="E12" s="257" t="n">
-        <f aca="false">Drivers!F111/(Drivers!F111+Drivers!F113)</f>
+        <f aca="false">Drivers!F111/SUM(Drivers!F111,Drivers!F113)</f>
         <v>0.788438358682679</v>
       </c>
       <c r="F12" s="257" t="n">
-        <f aca="false">Drivers!G111/(Drivers!G111+Drivers!G113)</f>
+        <f aca="false">Drivers!G111/SUM(Drivers!G111,Drivers!G113)</f>
         <v>0.818518450752578</v>
       </c>
       <c r="G12" s="257" t="n">
-        <f aca="false">Drivers!H111/(Drivers!H111+Drivers!H113)</f>
+        <f aca="false">Drivers!H111/SUM(Drivers!H111,Drivers!H113)</f>
         <v>0.857786620038572</v>
       </c>
       <c r="H12" s="257" t="n">
-        <f aca="false">Drivers!I111/(Drivers!I111+Drivers!I113)</f>
+        <f aca="false">Drivers!I111/SUM(Drivers!I111,Drivers!I113)</f>
         <v>0.854228877277724</v>
       </c>
       <c r="I12" s="257" t="n">
-        <f aca="false">Drivers!J111/(Drivers!J111+Drivers!J113)</f>
+        <f aca="false">Drivers!J111/SUM(Drivers!J111,Drivers!J113)</f>
         <v>0.855644874084143</v>
       </c>
     </row>
@@ -42777,23 +42803,23 @@
         <v>302</v>
       </c>
       <c r="F11" s="239" t="n">
-        <f aca="false">INDEX($C$143:$E$143,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$143,$D$143,$E$143)</f>
         <v>0.02</v>
       </c>
       <c r="G11" s="239" t="n">
-        <f aca="false">INDEX($C$143:$E$143,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$143,$D$143,$E$143)</f>
         <v>0.02</v>
       </c>
       <c r="H11" s="239" t="n">
-        <f aca="false">INDEX($C$143:$E$143,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$143,$D$143,$E$143)</f>
         <v>0.02</v>
       </c>
       <c r="I11" s="239" t="n">
-        <f aca="false">INDEX($C$143:$E$143,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$143,$D$143,$E$143)</f>
         <v>0.02</v>
       </c>
       <c r="J11" s="239" t="n">
-        <f aca="false">INDEX($C$143:$E$143,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$143,$D$143,$E$143)</f>
         <v>0.02</v>
       </c>
       <c r="K11" s="280" t="s">
@@ -42859,23 +42885,23 @@
         <v>0.58</v>
       </c>
       <c r="F13" s="239" t="n">
-        <f aca="false">IF($C$4=2027,F149,F150)*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">IF($C$4=2027,F149,F150)*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.32</v>
       </c>
       <c r="G13" s="239" t="n">
-        <f aca="false">IF($C$4=2027,G149,G150)*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">IF($C$4=2027,G149,G150)*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.22</v>
       </c>
       <c r="H13" s="239" t="n">
-        <f aca="false">IF($C$4=2027,H149,H150)*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">IF($C$4=2027,H149,H150)*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.35</v>
       </c>
       <c r="I13" s="239" t="n">
-        <f aca="false">IF($C$4=2027,I149,I150)*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">IF($C$4=2027,I149,I150)*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.25</v>
       </c>
       <c r="J13" s="239" t="n">
-        <f aca="false">IF($C$4=2027,J149,J150)*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">IF($C$4=2027,J149,J150)*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.17</v>
       </c>
       <c r="K13" s="280" t="s">
@@ -43045,23 +43071,23 @@
         <v>0.395</v>
       </c>
       <c r="F20" s="239" t="n">
-        <f aca="false">F151*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">F151*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.22</v>
       </c>
       <c r="G20" s="239" t="n">
-        <f aca="false">G151*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">G151*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.18</v>
       </c>
       <c r="H20" s="239" t="n">
-        <f aca="false">H151*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">H151*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.28</v>
       </c>
       <c r="I20" s="239" t="n">
-        <f aca="false">I151*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">I151*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.2</v>
       </c>
       <c r="J20" s="239" t="n">
-        <f aca="false">J151*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">J151*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.15</v>
       </c>
       <c r="K20" s="280" t="s">
@@ -43155,23 +43181,23 @@
         <v>302</v>
       </c>
       <c r="F25" s="239" t="n">
-        <f aca="false">INDEX($C$144:$E$144,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$144,$D$144,$E$144)</f>
         <v>0.015</v>
       </c>
       <c r="G25" s="239" t="n">
-        <f aca="false">INDEX($C$144:$E$144,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$144,$D$144,$E$144)</f>
         <v>0.015</v>
       </c>
       <c r="H25" s="239" t="n">
-        <f aca="false">INDEX($C$144:$E$144,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$144,$D$144,$E$144)</f>
         <v>0.015</v>
       </c>
       <c r="I25" s="239" t="n">
-        <f aca="false">INDEX($C$144:$E$144,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$144,$D$144,$E$144)</f>
         <v>0.015</v>
       </c>
       <c r="J25" s="239" t="n">
-        <f aca="false">INDEX($C$144:$E$144,$C$3)</f>
+        <f aca="false">CHOOSE($C$3,$C$144,$D$144,$E$144)</f>
         <v>0.015</v>
       </c>
       <c r="K25" s="280" t="s">
@@ -43234,23 +43260,23 @@
         <v>0.2</v>
       </c>
       <c r="F27" s="239" t="n">
-        <f aca="false">F152*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">F152*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.3</v>
       </c>
       <c r="G27" s="239" t="n">
-        <f aca="false">G152*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">G152*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.3</v>
       </c>
       <c r="H27" s="239" t="n">
-        <f aca="false">H152*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">H152*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.4</v>
       </c>
       <c r="I27" s="239" t="n">
-        <f aca="false">I152*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">I152*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.32</v>
       </c>
       <c r="J27" s="239" t="n">
-        <f aca="false">J152*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">J152*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.25</v>
       </c>
       <c r="K27" s="280" t="s">
@@ -43416,23 +43442,23 @@
         <v>1.1</v>
       </c>
       <c r="F34" s="239" t="n">
-        <f aca="false">F153*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">F153*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.6</v>
       </c>
       <c r="G34" s="239" t="n">
-        <f aca="false">G153*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">G153*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.5</v>
       </c>
       <c r="H34" s="239" t="n">
-        <f aca="false">H153*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">H153*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.7</v>
       </c>
       <c r="I34" s="239" t="n">
-        <f aca="false">I153*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">I153*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.45</v>
       </c>
       <c r="J34" s="239" t="n">
-        <f aca="false">J153*INDEX($C$142:$E$142,$C$3)</f>
+        <f aca="false">J153*CHOOSE($C$3,$C$142,$D$142,$E$142)</f>
         <v>0.3</v>
       </c>
       <c r="K34" s="280" t="s">
@@ -43487,35 +43513,35 @@
         <v>311</v>
       </c>
       <c r="C37" s="283" t="n">
-        <f aca="false">C14+C21+C28+C35</f>
+        <f aca="false">SUM(C14,C21,C28,C35)</f>
         <v>19595000</v>
       </c>
       <c r="D37" s="283" t="n">
-        <f aca="false">D14+D21+D28+D35</f>
+        <f aca="false">SUM(D14,D21,D28,D35)</f>
         <v>31162000</v>
       </c>
       <c r="E37" s="283" t="n">
-        <f aca="false">E14+E21+E28+E35</f>
+        <f aca="false">SUM(E14,E21,E28,E35)</f>
         <v>47881700</v>
       </c>
       <c r="F37" s="283" t="n">
-        <f aca="false">F14+F21+F28+F35</f>
+        <f aca="false">SUM(F14,F21,F28,F35)</f>
         <v>64122675.72</v>
       </c>
       <c r="G37" s="283" t="n">
-        <f aca="false">G14+G21+G28+G35</f>
+        <f aca="false">SUM(G14,G21,G28,G35)</f>
         <v>80302739.2577568</v>
       </c>
       <c r="H37" s="283" t="n">
-        <f aca="false">H14+H21+H28+H35</f>
+        <f aca="false">SUM(H14,H21,H28,H35)</f>
         <v>111179924.390085</v>
       </c>
       <c r="I37" s="283" t="n">
-        <f aca="false">I14+I21+I28+I35</f>
+        <f aca="false">SUM(I14,I21,I28,I35)</f>
         <v>142602550.441542</v>
       </c>
       <c r="J37" s="283" t="n">
-        <f aca="false">J14+J21+J28+J35</f>
+        <f aca="false">SUM(J14,J21,J28,J35)</f>
         <v>171518376.683189</v>
       </c>
     </row>
@@ -43618,7 +43644,7 @@
       </c>
       <c r="G40" s="285" t="n">
         <f aca="false">G39/F39-1</f>
-        <v>0.252329824918865</v>
+        <v>0.252329824918866</v>
       </c>
       <c r="H40" s="285" t="n">
         <f aca="false">H39/G39-1</f>
@@ -43686,35 +43712,35 @@
         <v>311</v>
       </c>
       <c r="C44" s="281" t="n">
-        <f aca="false">(SUM('Balance Sheet'!D29:D31)+C96)/2</f>
+        <f aca="false">SUM('Balance Sheet'!D29:D31,C96)/2</f>
         <v>17289500</v>
       </c>
       <c r="D44" s="281" t="n">
-        <f aca="false">(C96+D96)/2</f>
+        <f aca="false">SUM(C96:D96)/2</f>
         <v>22946800</v>
       </c>
       <c r="E44" s="281" t="n">
-        <f aca="false">(D96+E96)/2</f>
+        <f aca="false">SUM(D96:E96)/2</f>
         <v>28641860</v>
       </c>
       <c r="F44" s="281" t="n">
-        <f aca="false">(E96+F96)/2</f>
+        <f aca="false">SUM(E96:F96)/2</f>
         <v>37551501.698996</v>
       </c>
       <c r="G44" s="281" t="n">
-        <f aca="false">(F96+G96)/2</f>
+        <f aca="false">SUM(F96:G96)/2</f>
         <v>69834584.9249516</v>
       </c>
       <c r="H44" s="281" t="n">
-        <f aca="false">(G96+H96)/2</f>
+        <f aca="false">SUM(G96:H96)/2</f>
         <v>102374386.347072</v>
       </c>
       <c r="I44" s="281" t="n">
-        <f aca="false">(H96+I96)/2</f>
+        <f aca="false">SUM(H96:I96)/2</f>
         <v>116078702.871656</v>
       </c>
       <c r="J44" s="281" t="n">
-        <f aca="false">(I96+J96)/2</f>
+        <f aca="false">SUM(I96:J96)/2</f>
         <v>131674806.903399</v>
       </c>
     </row>
@@ -43996,23 +44022,23 @@
         <v>0.245</v>
       </c>
       <c r="F54" s="239" t="n">
-        <f aca="false">F154+INDEX($C$145:$E$145,$C$3)</f>
+        <f aca="false">F154+CHOOSE($C$3,$C$145,$D$145,$E$145)</f>
         <v>0.25</v>
       </c>
       <c r="G54" s="239" t="n">
-        <f aca="false">G154+INDEX($C$145:$E$145,$C$3)</f>
+        <f aca="false">G154+CHOOSE($C$3,$C$145,$D$145,$E$145)</f>
         <v>0.255</v>
       </c>
       <c r="H54" s="239" t="n">
-        <f aca="false">H154+INDEX($C$145:$E$145,$C$3)</f>
+        <f aca="false">H154+CHOOSE($C$3,$C$145,$D$145,$E$145)</f>
         <v>0.27</v>
       </c>
       <c r="I54" s="239" t="n">
-        <f aca="false">I154+INDEX($C$145:$E$145,$C$3)</f>
+        <f aca="false">I154+CHOOSE($C$3,$C$145,$D$145,$E$145)</f>
         <v>0.265</v>
       </c>
       <c r="J54" s="239" t="n">
-        <f aca="false">J154+INDEX($C$145:$E$145,$C$3)</f>
+        <f aca="false">J154+CHOOSE($C$3,$C$145,$D$145,$E$145)</f>
         <v>0.27</v>
       </c>
       <c r="K54" s="280" t="s">
@@ -44172,35 +44198,35 @@
         <v>311</v>
       </c>
       <c r="C59" s="283" t="n">
-        <f aca="false">C55+C56</f>
+        <f aca="false">SUM(C55:C56)</f>
         <v>6011751.2</v>
       </c>
       <c r="D59" s="283" t="n">
-        <f aca="false">D55+D56</f>
+        <f aca="false">SUM(D55:D56)</f>
         <v>8892571.25</v>
       </c>
       <c r="E59" s="283" t="n">
-        <f aca="false">E55+E56</f>
+        <f aca="false">SUM(E55:E56)</f>
         <v>12925449.3845</v>
       </c>
       <c r="F59" s="283" t="n">
-        <f aca="false">F55+F56</f>
+        <f aca="false">SUM(F55:F56)</f>
         <v>17322659.24749</v>
       </c>
       <c r="G59" s="283" t="n">
-        <f aca="false">G55+G56</f>
+        <f aca="false">SUM(G55:G56)</f>
         <v>21878483.6211529</v>
       </c>
       <c r="H59" s="283" t="n">
-        <f aca="false">H55+H56</f>
+        <f aca="false">SUM(H55:H56)</f>
         <v>32407537.5782256</v>
       </c>
       <c r="I59" s="283" t="n">
-        <f aca="false">I55+I56</f>
+        <f aca="false">SUM(I55:I56)</f>
         <v>40384144.9909396</v>
       </c>
       <c r="J59" s="283" t="n">
-        <f aca="false">J55+J56</f>
+        <f aca="false">SUM(J55:J56)</f>
         <v>49130688.5130299</v>
       </c>
       <c r="K59" s="247" t="s">
@@ -44227,23 +44253,23 @@
         <v>0.226466167568605</v>
       </c>
       <c r="F61" s="239" t="n">
-        <f aca="false">F155+INDEX($C$146:$E$146,$C$3)</f>
+        <f aca="false">F155+CHOOSE($C$3,$C$146,$D$146,$E$146)</f>
         <v>0.225</v>
       </c>
       <c r="G61" s="239" t="n">
-        <f aca="false">G155+INDEX($C$146:$E$146,$C$3)</f>
+        <f aca="false">G155+CHOOSE($C$3,$C$146,$D$146,$E$146)</f>
         <v>0.23</v>
       </c>
       <c r="H61" s="239" t="n">
-        <f aca="false">H155+INDEX($C$146:$E$146,$C$3)</f>
+        <f aca="false">H155+CHOOSE($C$3,$C$146,$D$146,$E$146)</f>
         <v>0.235</v>
       </c>
       <c r="I61" s="239" t="n">
-        <f aca="false">I155+INDEX($C$146:$E$146,$C$3)</f>
+        <f aca="false">I155+CHOOSE($C$3,$C$146,$D$146,$E$146)</f>
         <v>0.23</v>
       </c>
       <c r="J61" s="239" t="n">
-        <f aca="false">J155+INDEX($C$146:$E$146,$C$3)</f>
+        <f aca="false">J155+CHOOSE($C$3,$C$146,$D$146,$E$146)</f>
         <v>0.225</v>
       </c>
       <c r="K61" s="280" t="s">
@@ -44588,7 +44614,7 @@
       </c>
       <c r="G70" s="281" t="n">
         <f aca="false">G39*G69</f>
-        <v>3987031.00414762</v>
+        <v>3987031.00414763</v>
       </c>
       <c r="H70" s="281" t="n">
         <f aca="false">H39*H69</f>
@@ -44666,7 +44692,7 @@
       </c>
       <c r="G72" s="281" t="n">
         <f aca="false">G39*G71</f>
-        <v>2392218.60248857</v>
+        <v>2392218.60248858</v>
       </c>
       <c r="H72" s="281" t="n">
         <f aca="false">H39*H71</f>
@@ -44678,7 +44704,7 @@
       </c>
       <c r="J72" s="281" t="n">
         <f aca="false">J39*J71</f>
-        <v>4768896.94529939</v>
+        <v>4768896.9452994</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -44761,36 +44787,36 @@
         <v>311</v>
       </c>
       <c r="C75" s="283" t="n">
-        <f aca="false">C62+C64+C66+C68+C70+C72+C74</f>
+        <f aca="false">SUM(C62,C64,C66,C68,C70,C72,C74)</f>
         <v>16189000</v>
       </c>
       <c r="D75" s="283" t="n">
-        <f aca="false">D62+D64+D66+D68+D70+D72+D74</f>
+        <f aca="false">SUM(D62,D64,D66,D68,D70,D72,D74)</f>
         <v>20021150</v>
       </c>
       <c r="E75" s="283" t="n">
-        <f aca="false">E62+E64+E66+E68+E70+E72+E74</f>
+        <f aca="false">SUM(E62,E64,E66,E68,E70,E72,E74)</f>
         <v>26926449.5</v>
       </c>
       <c r="F75" s="283" t="n">
-        <f aca="false">F62+F64+F66+F68+F70+F72+F74</f>
+        <f aca="false">SUM(F62,F64,F66,F68,F70,F72,F74)</f>
         <v>34966953.7078234</v>
       </c>
       <c r="G75" s="283" t="n">
-        <f aca="false">G62+G64+G66+G68+G70+G72+G74</f>
-        <v>43592361.879205</v>
+        <f aca="false">SUM(G62,G64,G66,G68,G70,G72,G74)</f>
+        <v>43592361.8792051</v>
       </c>
       <c r="H75" s="283" t="n">
-        <f aca="false">H62+H64+H66+H68+H70+H72+H74</f>
+        <f aca="false">SUM(H62,H64,H66,H68,H70,H72,H74)</f>
         <v>60236612.7780578</v>
       </c>
       <c r="I75" s="283" t="n">
-        <f aca="false">I62+I64+I66+I68+I70+I72+I74</f>
+        <f aca="false">SUM(I62,I64,I66,I68,I70,I72,I74)</f>
         <v>74293523.3450348</v>
       </c>
       <c r="J75" s="283" t="n">
-        <f aca="false">J62+J64+J66+J68+J70+J72+J74</f>
-        <v>86752425.1331408</v>
+        <f aca="false">SUM(J62,J64,J66,J68,J70,J72,J74)</f>
+        <v>86752425.1331409</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44966,35 +44992,35 @@
         <v>311</v>
       </c>
       <c r="C82" s="283" t="n">
-        <f aca="false">C59+C80+C81</f>
+        <f aca="false">SUM(C59,C80,C81)</f>
         <v>12195131.2</v>
       </c>
       <c r="D82" s="283" t="n">
-        <f aca="false">D59+D80+D81</f>
+        <f aca="false">SUM(D59,D80,D81)</f>
         <v>16414163.25</v>
       </c>
       <c r="E82" s="283" t="n">
-        <f aca="false">E59+E80+E81</f>
+        <f aca="false">SUM(E59,E80,E81)</f>
         <v>23281582.1845</v>
       </c>
       <c r="F82" s="283" t="n">
-        <f aca="false">F59+F80+F81</f>
+        <f aca="false">SUM(F59,F80,F81)</f>
         <v>30719170.3834087</v>
       </c>
       <c r="G82" s="283" t="n">
-        <f aca="false">G59+G80+G81</f>
+        <f aca="false">SUM(G59,G80,G81)</f>
         <v>39459962.8614914</v>
       </c>
       <c r="H82" s="283" t="n">
-        <f aca="false">H59+H80+H81</f>
+        <f aca="false">SUM(H59,H80,H81)</f>
         <v>60909642.3942658</v>
       </c>
       <c r="I82" s="283" t="n">
-        <f aca="false">I59+I80+I81</f>
+        <f aca="false">SUM(I59,I80,I81)</f>
         <v>74954279.0518415</v>
       </c>
       <c r="J82" s="283" t="n">
-        <f aca="false">J59+J80+J81</f>
+        <f aca="false">SUM(J59,J80,J81)</f>
         <v>89256897.1364555</v>
       </c>
     </row>
@@ -45035,7 +45061,7 @@
       </c>
       <c r="J83" s="239" t="n">
         <f aca="false">J82/J39</f>
-        <v>0.524061045664692</v>
+        <v>0.524061045664691</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45209,35 +45235,35 @@
         <v>311</v>
       </c>
       <c r="C88" s="283" t="n">
-        <f aca="false">C86+C64+C66+C68+C70+C72+C74+C87</f>
+        <f aca="false">SUM(C86,C64,C66,C68,C70,C72,C74,C87)</f>
         <v>11437820</v>
       </c>
       <c r="D88" s="283" t="n">
-        <f aca="false">D86+D64+D66+D68+D70+D72+D74+D87</f>
+        <f aca="false">SUM(D86,D64,D66,D68,D70,D72,D74,D87)</f>
         <v>14874838</v>
       </c>
       <c r="E88" s="283" t="n">
-        <f aca="false">E86+E64+E66+E68+E70+E72+E74+E87</f>
+        <f aca="false">SUM(E86,E64,E66,E68,E70,E72,E74,E87)</f>
         <v>19702268.7</v>
       </c>
       <c r="F88" s="283" t="n">
-        <f aca="false">F86+F64+F66+F68+F70+F72+F74+F87</f>
+        <f aca="false">SUM(F86,F64,F66,F68,F70,F72,F74,F87)</f>
         <v>25312536.9719047</v>
       </c>
       <c r="G88" s="283" t="n">
-        <f aca="false">G86+G64+G66+G68+G70+G72+G74+G87</f>
+        <f aca="false">SUM(G86,G64,G66,G68,G70,G72,G74,G87)</f>
         <v>31281148.6466256</v>
       </c>
       <c r="H88" s="283" t="n">
-        <f aca="false">H86+H64+H66+H68+H70+H72+H74+H87</f>
+        <f aca="false">SUM(H86,H64,H66,H68,H70,H72,H74,H87)</f>
         <v>43224542.3362469</v>
       </c>
       <c r="I88" s="283" t="n">
-        <f aca="false">I86+I64+I66+I68+I70+I72+I74+I87</f>
+        <f aca="false">SUM(I86,I64,I66,I68,I70,I72,I74,I87)</f>
         <v>52803207.6332009</v>
       </c>
       <c r="J88" s="283" t="n">
-        <f aca="false">J86+J64+J66+J68+J70+J72+J74+J87</f>
+        <f aca="false">SUM(J86,J64,J66,J68,J70,J72,J74,J87)</f>
         <v>61405286.8498447</v>
       </c>
     </row>
@@ -45302,11 +45328,11 @@
       </c>
       <c r="F90" s="283" t="n">
         <f aca="false">F39-F82-F88</f>
-        <v>7642109.63464663</v>
+        <v>7642109.63464664</v>
       </c>
       <c r="G90" s="283" t="n">
         <f aca="false">G39-G82-G88</f>
-        <v>8999508.57483552</v>
+        <v>8999508.57483553</v>
       </c>
       <c r="H90" s="283" t="n">
         <f aca="false">H39-H82-H88</f>
@@ -45465,23 +45491,23 @@
         <v>31184120</v>
       </c>
       <c r="F96" s="281" t="n">
-        <f aca="false">E96+F95</f>
+        <f aca="false">SUM(E96,F95)</f>
         <v>43918883.397992</v>
       </c>
       <c r="G96" s="281" t="n">
-        <f aca="false">F96+G95</f>
+        <f aca="false">SUM(F96,G95)</f>
         <v>95750286.4519111</v>
       </c>
       <c r="H96" s="281" t="n">
-        <f aca="false">G96+H95</f>
+        <f aca="false">SUM(G96,H95)</f>
         <v>108998486.242234</v>
       </c>
       <c r="I96" s="281" t="n">
-        <f aca="false">H96+I95</f>
+        <f aca="false">SUM(H96,I95)</f>
         <v>123158919.501079</v>
       </c>
       <c r="J96" s="281" t="n">
-        <f aca="false">I96+J95</f>
+        <f aca="false">SUM(I96,J95)</f>
         <v>140190694.305719</v>
       </c>
     </row>
@@ -45584,23 +45610,23 @@
         <v>9789432</v>
       </c>
       <c r="F99" s="281" t="n">
-        <f aca="false">E99+F98</f>
+        <f aca="false">SUM(E99,F98)</f>
         <v>13531526.4</v>
       </c>
       <c r="G99" s="281" t="n">
-        <f aca="false">F99+G98</f>
+        <f aca="false">SUM(F99,G98)</f>
         <v>18801792.407759</v>
       </c>
       <c r="H99" s="281" t="n">
-        <f aca="false">G99+H98</f>
+        <f aca="false">SUM(G99,H98)</f>
         <v>30291826.7819884</v>
       </c>
       <c r="I99" s="281" t="n">
-        <f aca="false">H99+I98</f>
+        <f aca="false">SUM(H99,I98)</f>
         <v>43371645.1310564</v>
       </c>
       <c r="J99" s="281" t="n">
-        <f aca="false">I99+J98</f>
+        <f aca="false">SUM(I99,J98)</f>
         <v>58150715.4711859</v>
       </c>
     </row>
@@ -46259,7 +46285,7 @@
       </c>
       <c r="G120" s="281" t="n">
         <f aca="false">G39*G119</f>
-        <v>3987031.00414762</v>
+        <v>3987031.00414763</v>
       </c>
       <c r="H120" s="281" t="n">
         <f aca="false">H39*H119</f>
@@ -46423,11 +46449,11 @@
       </c>
       <c r="I125" s="281" t="n">
         <f aca="false">IF(AND(I$7&gt;=$C$4+2,I$7&lt;=$C$4+6),SUM($F$124:$J$124)/5,0)</f>
-        <v>6219768.36647029</v>
+        <v>6219768.3664703</v>
       </c>
       <c r="J125" s="281" t="n">
         <f aca="false">IF(AND(J$7&gt;=$C$4+2,J$7&lt;=$C$4+6),SUM($F$124:$J$124)/5,0)</f>
-        <v>6219768.36647029</v>
+        <v>6219768.3664703</v>
       </c>
       <c r="K125" s="280" t="s">
         <v>440</v>
@@ -46487,23 +46513,23 @@
         <v>1500000</v>
       </c>
       <c r="F127" s="283" t="n">
-        <f aca="false">F122+F126</f>
+        <f aca="false">SUM(F122,F126)</f>
         <v>1500000</v>
       </c>
       <c r="G127" s="283" t="n">
-        <f aca="false">G122+G126</f>
+        <f aca="false">SUM(G122,G126)</f>
         <v>32598841.8323515</v>
       </c>
       <c r="H127" s="283" t="n">
-        <f aca="false">H122+H126</f>
+        <f aca="false">SUM(H122,H126)</f>
         <v>32598841.8323515</v>
       </c>
       <c r="I127" s="283" t="n">
-        <f aca="false">I122+I126</f>
+        <f aca="false">SUM(I122,I126)</f>
         <v>26379073.4658812</v>
       </c>
       <c r="J127" s="283" t="n">
-        <f aca="false">J122+J126</f>
+        <f aca="false">SUM(J122,J126)</f>
         <v>20159305.0994109</v>
       </c>
     </row>
@@ -46558,23 +46584,23 @@
         <v>142182</v>
       </c>
       <c r="F129" s="281" t="n">
-        <f aca="false">F128*((E121+E127)+(F121+F127))/2</f>
+        <f aca="false">F128*(SUM(E121,E127)+SUM(F121,F127))/2</f>
         <v>160260</v>
       </c>
       <c r="G129" s="281" t="n">
-        <f aca="false">G128*((F121+F127)+(G121+G127))/2</f>
+        <f aca="false">G128*(SUM(F121,F127)+SUM(G121,G127))/2</f>
         <v>1715202.09161757</v>
       </c>
       <c r="H129" s="281" t="n">
-        <f aca="false">H128*((G121+G127)+(H121+H127))/2</f>
+        <f aca="false">H128*(SUM(G121,G127)+SUM(H121,H127))/2</f>
         <v>3270144.18323515</v>
       </c>
       <c r="I129" s="281" t="n">
-        <f aca="false">I128*((H121+H127)+(I121+I127))/2</f>
+        <f aca="false">I128*(SUM(H121,H127)+SUM(I121,I127))/2</f>
         <v>2959155.76491163</v>
       </c>
       <c r="J129" s="281" t="n">
-        <f aca="false">J128*((I121+I127)+(J121+J127))/2</f>
+        <f aca="false">J128*(SUM(I121,I127)+SUM(J121,J127))/2</f>
         <v>2337178.9282646</v>
       </c>
       <c r="K129" s="247" t="s">
@@ -46787,7 +46813,7 @@
       </c>
       <c r="G136" s="289" t="n">
         <f aca="false">'Income Statement'!F76</f>
-        <v>7284306.48321796</v>
+        <v>7284306.48321795</v>
       </c>
       <c r="H136" s="289" t="n">
         <f aca="false">'Income Statement'!G76</f>
@@ -46810,15 +46836,15 @@
         <v>311</v>
       </c>
       <c r="C137" s="282" t="n">
-        <f aca="false">N('Income Statement'!B78)</f>
+        <f aca="false">'Income Statement'!B78</f>
         <v>0</v>
       </c>
       <c r="D137" s="282" t="n">
-        <f aca="false">N('Income Statement'!C78)</f>
+        <f aca="false">'Income Statement'!C78</f>
         <v>0</v>
       </c>
       <c r="E137" s="282" t="n">
-        <f aca="false">N('Income Statement'!D78)</f>
+        <f aca="false">'Income Statement'!D78</f>
         <v>0</v>
       </c>
       <c r="F137" s="283" t="n">
@@ -47562,15 +47588,15 @@
       </c>
       <c r="C10" s="309" t="n">
         <f aca="false">C6-C7-C8</f>
-        <v>7642109.63464663</v>
+        <v>7642109.63464664</v>
       </c>
       <c r="D10" s="309" t="n">
         <f aca="false">D6-D7-D8</f>
-        <v>8999508.57483552</v>
+        <v>8999508.57483553</v>
       </c>
       <c r="E10" s="309" t="n">
         <f aca="false">E6-E7-E8</f>
-        <v>6267480.18884142</v>
+        <v>6267480.18884141</v>
       </c>
       <c r="F10" s="309" t="n">
         <f aca="false">F6-F7-F8</f>
@@ -47622,15 +47648,15 @@
       </c>
       <c r="C12" s="317" t="n">
         <f aca="false">C10-C11</f>
-        <v>7481849.63464663</v>
+        <v>7481849.63464664</v>
       </c>
       <c r="D12" s="317" t="n">
         <f aca="false">D10-D11</f>
-        <v>7284306.48321794</v>
+        <v>7284306.48321796</v>
       </c>
       <c r="E12" s="317" t="n">
         <f aca="false">E10-E11</f>
-        <v>2997336.00560627</v>
+        <v>2997336.00560626</v>
       </c>
       <c r="F12" s="317" t="n">
         <f aca="false">F10-F11</f>
@@ -47681,23 +47707,23 @@
       </c>
       <c r="C14" s="309" t="n">
         <f aca="false">C12-C13</f>
-        <v>6579139.8766217</v>
+        <v>6579139.87662171</v>
       </c>
       <c r="D14" s="309" t="n">
         <f aca="false">D12-D13</f>
-        <v>5827445.18657435</v>
+        <v>5827445.18657437</v>
       </c>
       <c r="E14" s="309" t="n">
         <f aca="false">E12-E13</f>
-        <v>2397868.80448502</v>
+        <v>2397868.80448501</v>
       </c>
       <c r="F14" s="309" t="n">
         <f aca="false">F12-F13</f>
-        <v>8710152.11079785</v>
+        <v>8710152.11079786</v>
       </c>
       <c r="G14" s="309" t="n">
         <f aca="false">G12-G13</f>
-        <v>13854708.1054737</v>
+        <v>13854708.1054738</v>
       </c>
       <c r="H14" s="310"/>
     </row>
@@ -47799,23 +47825,23 @@
         <v>31184120</v>
       </c>
       <c r="C22" s="306" t="n">
-        <f aca="false">B22+C25</f>
+        <f aca="false">SUM(B22,C25)</f>
         <v>43918883.397992</v>
       </c>
       <c r="D22" s="306" t="n">
-        <f aca="false">C22+D25</f>
+        <f aca="false">SUM(C22,D25)</f>
         <v>95750286.4519111</v>
       </c>
       <c r="E22" s="306" t="n">
-        <f aca="false">D22+E25</f>
+        <f aca="false">SUM(D22,E25)</f>
         <v>108998486.242234</v>
       </c>
       <c r="F22" s="306" t="n">
-        <f aca="false">E22+F25</f>
+        <f aca="false">SUM(E22,F25)</f>
         <v>123158919.501079</v>
       </c>
       <c r="G22" s="306" t="n">
-        <f aca="false">F22+G25</f>
+        <f aca="false">SUM(F22,G25)</f>
         <v>140190694.305719</v>
       </c>
       <c r="H22" s="320"/>
@@ -47829,23 +47855,23 @@
         <v>9789432</v>
       </c>
       <c r="C23" s="314" t="n">
-        <f aca="false">B23+C9</f>
+        <f aca="false">SUM(B23,C9)</f>
         <v>13531526.4</v>
       </c>
       <c r="D23" s="314" t="n">
-        <f aca="false">C23+D9</f>
+        <f aca="false">SUM(C23,D9)</f>
         <v>18801792.407759</v>
       </c>
       <c r="E23" s="314" t="n">
-        <f aca="false">D23+E9</f>
+        <f aca="false">SUM(D23,E9)</f>
         <v>30291826.7819884</v>
       </c>
       <c r="F23" s="314" t="n">
-        <f aca="false">E23+F9</f>
+        <f aca="false">SUM(E23,F9)</f>
         <v>43371645.1310564</v>
       </c>
       <c r="G23" s="314" t="n">
-        <f aca="false">F23+G9</f>
+        <f aca="false">SUM(F23,G9)</f>
         <v>58150715.4711859</v>
       </c>
       <c r="H23" s="305"/>
@@ -48132,7 +48158,7 @@
       </c>
       <c r="C36" s="336" t="n">
         <f aca="false">C31-C34</f>
-        <v>9831024.3280661</v>
+        <v>9831024.32806609</v>
       </c>
       <c r="D36" s="336" t="n">
         <f aca="false">D31-D34</f>
@@ -48159,11 +48185,11 @@
       <c r="B37" s="337"/>
       <c r="C37" s="337" t="n">
         <f aca="false">C36-B36</f>
-        <v>2584386.32806609</v>
+        <v>2584386.32806608</v>
       </c>
       <c r="D37" s="337" t="n">
         <f aca="false">D36-C36</f>
-        <v>3280215.67477489</v>
+        <v>3280215.6747749</v>
       </c>
       <c r="E37" s="337" t="n">
         <f aca="false">E36-D36</f>
@@ -48289,23 +48315,23 @@
       </c>
       <c r="C45" s="305" t="n">
         <f aca="false">C14</f>
-        <v>6579139.8766217</v>
+        <v>6579139.87662171</v>
       </c>
       <c r="D45" s="305" t="n">
         <f aca="false">D14</f>
-        <v>5827445.18657435</v>
+        <v>5827445.18657437</v>
       </c>
       <c r="E45" s="305" t="n">
         <f aca="false">E14</f>
-        <v>2397868.80448502</v>
+        <v>2397868.80448501</v>
       </c>
       <c r="F45" s="305" t="n">
         <f aca="false">F14</f>
-        <v>8710152.11079785</v>
+        <v>8710152.11079786</v>
       </c>
       <c r="G45" s="305" t="n">
         <f aca="false">G14</f>
-        <v>13854708.1054737</v>
+        <v>13854708.1054738</v>
       </c>
       <c r="H45" s="305"/>
     </row>
@@ -48354,7 +48380,7 @@
       </c>
       <c r="D47" s="305" t="n">
         <f aca="false">C31-D31</f>
-        <v>-3557048.48912234</v>
+        <v>-3557048.48912235</v>
       </c>
       <c r="E47" s="305" t="n">
         <f aca="false">D31-E31</f>
@@ -48362,11 +48388,11 @@
       </c>
       <c r="F47" s="305" t="n">
         <f aca="false">E31-F31</f>
-        <v>-6764023.81123132</v>
+        <v>-6764023.81123131</v>
       </c>
       <c r="G47" s="305" t="n">
         <f aca="false">F31-G31</f>
-        <v>-5231833.53169505</v>
+        <v>-5231833.53169506</v>
       </c>
       <c r="H47" s="305"/>
     </row>
@@ -48410,15 +48436,15 @@
       </c>
       <c r="C49" s="305" t="n">
         <f aca="false">SUM(C45:C48)</f>
-        <v>7736847.94855562</v>
+        <v>7736847.94855563</v>
       </c>
       <c r="D49" s="305" t="n">
         <f aca="false">SUM(D45:D48)</f>
-        <v>7817495.5195585</v>
+        <v>7817495.51955851</v>
       </c>
       <c r="E49" s="305" t="n">
         <f aca="false">SUM(E45:E48)</f>
-        <v>6948752.05176094</v>
+        <v>6948752.05176093</v>
       </c>
       <c r="F49" s="305" t="n">
         <f aca="false">SUM(F45:F48)</f>
@@ -48500,11 +48526,11 @@
       </c>
       <c r="F53" s="305" t="n">
         <f aca="false">(Drivers!I121-Drivers!H121)+(Drivers!I127-Drivers!H127)</f>
-        <v>-6219768.36647029</v>
+        <v>-6219768.3664703</v>
       </c>
       <c r="G53" s="305" t="n">
         <f aca="false">(Drivers!J121-Drivers!I121)+(Drivers!J127-Drivers!I127)</f>
-        <v>-6219768.36647029</v>
+        <v>-6219768.3664703</v>
       </c>
       <c r="H53" s="321"/>
     </row>
@@ -48532,7 +48558,7 @@
       </c>
       <c r="D55" s="349" t="n">
         <f aca="false">C59</f>
-        <v>-2064433.68393639</v>
+        <v>-2064433.68393638</v>
       </c>
       <c r="E55" s="349" t="n">
         <f aca="false">D59</f>
@@ -48561,24 +48587,24 @@
         <v>1197949.21549999</v>
       </c>
       <c r="C57" s="294" t="n">
-        <f aca="false">C49+C51+C53</f>
-        <v>-4997915.44943638</v>
+        <f aca="false">SUM(C49,C51,C53)</f>
+        <v>-4997915.44943637</v>
       </c>
       <c r="D57" s="294" t="n">
-        <f aca="false">D49+D51+D53</f>
+        <f aca="false">SUM(D49,D51,D53)</f>
         <v>-12915065.7020091</v>
       </c>
       <c r="E57" s="294" t="n">
-        <f aca="false">E49+E51+E53</f>
-        <v>-6299447.73856155</v>
+        <f aca="false">SUM(E49,E51,E53)</f>
+        <v>-6299447.73856157</v>
       </c>
       <c r="F57" s="294" t="n">
-        <f aca="false">F49+F51+F53</f>
-        <v>-4964043.85725853</v>
+        <f aca="false">SUM(F49,F51,F53)</f>
+        <v>-4964043.85725852</v>
       </c>
       <c r="G57" s="294" t="n">
-        <f aca="false">G49+G51+G53</f>
-        <v>567275.567771573</v>
+        <f aca="false">SUM(G49,G51,G53)</f>
+        <v>567275.567771565</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48593,23 +48619,23 @@
         <v>2933481.76549999</v>
       </c>
       <c r="C59" s="353" t="n">
-        <f aca="false">C55+C57</f>
-        <v>-2064433.68393639</v>
+        <f aca="false">SUM(C55,C57)</f>
+        <v>-2064433.68393638</v>
       </c>
       <c r="D59" s="353" t="n">
-        <f aca="false">D55+D57</f>
+        <f aca="false">SUM(D55,D57)</f>
         <v>-14979499.3859455</v>
       </c>
       <c r="E59" s="353" t="n">
-        <f aca="false">E55+E57</f>
+        <f aca="false">SUM(E55,E57)</f>
         <v>-21278947.1245071</v>
       </c>
       <c r="F59" s="353" t="n">
-        <f aca="false">F55+F57</f>
+        <f aca="false">SUM(F55,F57)</f>
         <v>-26242990.9817656</v>
       </c>
       <c r="G59" s="353" t="n">
-        <f aca="false">G55+G57</f>
+        <f aca="false">SUM(G55,G57)</f>
         <v>-25675715.413994</v>
       </c>
     </row>
@@ -48619,7 +48645,7 @@
       </c>
       <c r="C60" s="355" t="n">
         <f aca="false">MAX(0,Drivers!F120-C59)</f>
-        <v>5248124.53343439</v>
+        <v>5248124.53343438</v>
       </c>
       <c r="D60" s="355" t="n">
         <f aca="false">MAX(0,Drivers!G120-D59)</f>
@@ -48663,7 +48689,7 @@
         <v>541</v>
       </c>
       <c r="B63" s="360" t="n">
-        <f aca="false">B61+B62</f>
+        <f aca="false">SUM(B61:B62)</f>
         <v>37610763.0979458</v>
       </c>
       <c r="C63" s="293"/>
